--- a/www/flightdata/xlsx/eoss-369.xlsx
+++ b/www/flightdata/xlsx/eoss-369.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1649" uniqueCount="593">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1652" uniqueCount="595">
   <si>
     <t>flight</t>
   </si>
@@ -228,6 +228,9 @@
     <t>velocity_curvefit</t>
   </si>
   <si>
+    <t>reynolds_transition</t>
+  </si>
+  <si>
     <t>AE0SS-4</t>
   </si>
   <si>
@@ -1195,6 +1198,9 @@
   </si>
   <si>
     <t>low Re</t>
+  </si>
+  <si>
+    <t>high_to_low</t>
   </si>
   <si>
     <t>descending</t>
@@ -2320,10 +2326,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE160"/>
+  <dimension ref="A1:AF160"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:32">
       <c r="A1" s="1" t="s">
         <v>39</v>
       </c>
@@ -2417,13 +2423,16 @@
       <c r="AE1" s="1" t="s">
         <v>69</v>
       </c>
+      <c r="AF1" s="1" t="s">
+        <v>70</v>
+      </c>
     </row>
-    <row r="2" spans="1:31">
+    <row r="2" spans="1:32">
       <c r="A2" t="s">
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C2" s="2">
         <v>45739.29220704861</v>
@@ -2441,13 +2450,13 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K2">
         <v>348</v>
@@ -2486,7 +2495,7 @@
         <v>1.03333333</v>
       </c>
       <c r="W2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Y2">
         <v>1.033333</v>
@@ -2495,12 +2504,12 @@
         <v>7.190805</v>
       </c>
     </row>
-    <row r="3" spans="1:31">
+    <row r="3" spans="1:32">
       <c r="A3" t="s">
         <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C3" s="2">
         <v>45739.29250505787</v>
@@ -2518,13 +2527,13 @@
         <v>26</v>
       </c>
       <c r="H3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K3">
         <v>163</v>
@@ -2563,7 +2572,7 @@
         <v>8.4</v>
       </c>
       <c r="W3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X3">
         <v>0.245556</v>
@@ -2584,12 +2593,12 @@
         <v>10.283738</v>
       </c>
     </row>
-    <row r="4" spans="1:31">
+    <row r="4" spans="1:32">
       <c r="A4" t="s">
         <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C4" s="2">
         <v>45739.29258331018</v>
@@ -2607,13 +2616,13 @@
         <v>30</v>
       </c>
       <c r="H4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K4">
         <v>215</v>
@@ -2652,7 +2661,7 @@
         <v>10</v>
       </c>
       <c r="W4" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X4">
         <v>0.053333</v>
@@ -2679,12 +2688,12 @@
         <v>11.118406</v>
       </c>
     </row>
-    <row r="5" spans="1:31">
+    <row r="5" spans="1:32">
       <c r="A5" t="s">
         <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C5" s="2">
         <v>45739.29287907408</v>
@@ -2702,13 +2711,13 @@
         <v>56</v>
       </c>
       <c r="H5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J5" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K5">
         <v>200</v>
@@ -2747,7 +2756,7 @@
         <v>25.2</v>
       </c>
       <c r="W5" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X5">
         <v>0.506667</v>
@@ -2774,12 +2783,12 @@
         <v>17.962085</v>
       </c>
     </row>
-    <row r="6" spans="1:31">
+    <row r="6" spans="1:32">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C6" s="2">
         <v>45739.29290181713</v>
@@ -2797,13 +2806,13 @@
         <v>60</v>
       </c>
       <c r="H6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K6">
         <v>194</v>
@@ -2842,7 +2851,7 @@
         <v>24.23333333</v>
       </c>
       <c r="W6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X6">
         <v>-0.032222</v>
@@ -2869,12 +2878,12 @@
         <v>18.272088</v>
       </c>
     </row>
-    <row r="7" spans="1:31">
+    <row r="7" spans="1:32">
       <c r="A7" t="s">
         <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C7" s="2">
         <v>45739.29319762732</v>
@@ -2892,13 +2901,13 @@
         <v>86</v>
       </c>
       <c r="H7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J7" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K7">
         <v>171</v>
@@ -2937,7 +2946,7 @@
         <v>24.96666667</v>
       </c>
       <c r="W7" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X7">
         <v>0.024444</v>
@@ -2964,12 +2973,12 @@
         <v>22.733875</v>
       </c>
     </row>
-    <row r="8" spans="1:31">
+    <row r="8" spans="1:32">
       <c r="A8" t="s">
         <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C8" s="2">
         <v>45739.29327443287</v>
@@ -2987,13 +2996,13 @@
         <v>90</v>
       </c>
       <c r="H8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K8">
         <v>196</v>
@@ -3032,7 +3041,7 @@
         <v>25</v>
       </c>
       <c r="W8" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X8">
         <v>0.001111</v>
@@ -3059,12 +3068,12 @@
         <v>22.926209</v>
       </c>
     </row>
-    <row r="9" spans="1:31">
+    <row r="9" spans="1:32">
       <c r="A9" t="s">
         <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C9" s="2">
         <v>45739.29357415509</v>
@@ -3082,13 +3091,13 @@
         <v>116</v>
       </c>
       <c r="H9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K9">
         <v>166</v>
@@ -3127,7 +3136,7 @@
         <v>25.63333333</v>
       </c>
       <c r="W9" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X9">
         <v>0.021111</v>
@@ -3154,12 +3163,12 @@
         <v>25.56285</v>
       </c>
     </row>
-    <row r="10" spans="1:31">
+    <row r="10" spans="1:32">
       <c r="A10" t="s">
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" s="2">
         <v>45739.29359322917</v>
@@ -3177,13 +3186,13 @@
         <v>120</v>
       </c>
       <c r="H10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K10">
         <v>159</v>
@@ -3222,7 +3231,7 @@
         <v>25.86666667</v>
       </c>
       <c r="W10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X10">
         <v>0.007778</v>
@@ -3249,12 +3258,12 @@
         <v>25.683646</v>
       </c>
     </row>
-    <row r="11" spans="1:31">
+    <row r="11" spans="1:32">
       <c r="A11" t="s">
         <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C11" s="2">
         <v>45739.29389310185</v>
@@ -3272,13 +3281,13 @@
         <v>146</v>
       </c>
       <c r="H11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K11">
         <v>152</v>
@@ -3317,7 +3326,7 @@
         <v>26.03333333</v>
       </c>
       <c r="W11" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X11">
         <v>0.005556</v>
@@ -3344,12 +3353,12 @@
         <v>26.981314</v>
       </c>
     </row>
-    <row r="12" spans="1:31">
+    <row r="12" spans="1:32">
       <c r="A12" t="s">
         <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C12" s="2">
         <v>45739.29396958333</v>
@@ -3367,13 +3376,13 @@
         <v>150</v>
       </c>
       <c r="H12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J12" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K12">
         <v>133</v>
@@ -3412,7 +3421,7 @@
         <v>26.16666667</v>
       </c>
       <c r="W12" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X12">
         <v>0.004444</v>
@@ -3439,12 +3448,12 @@
         <v>27.036444</v>
       </c>
     </row>
-    <row r="13" spans="1:31">
+    <row r="13" spans="1:32">
       <c r="A13" t="s">
         <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C13" s="2">
         <v>45739.29427015047</v>
@@ -3462,13 +3471,13 @@
         <v>176</v>
       </c>
       <c r="H13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J13" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K13">
         <v>128</v>
@@ -3507,7 +3516,7 @@
         <v>25.03333333</v>
       </c>
       <c r="W13" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X13">
         <v>-0.037778</v>
@@ -3534,12 +3543,12 @@
         <v>27.455414</v>
       </c>
     </row>
-    <row r="14" spans="1:31">
+    <row r="14" spans="1:32">
       <c r="A14" t="s">
         <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C14" s="2">
         <v>45739.29428724537</v>
@@ -3557,13 +3566,13 @@
         <v>180</v>
       </c>
       <c r="H14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K14">
         <v>123</v>
@@ -3602,7 +3611,7 @@
         <v>24.9</v>
       </c>
       <c r="W14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X14">
         <v>-0.004444</v>
@@ -3629,12 +3638,12 @@
         <v>27.464718</v>
       </c>
     </row>
-    <row r="15" spans="1:31">
+    <row r="15" spans="1:32">
       <c r="A15" t="s">
         <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C15" s="2">
         <v>45739.29458950231</v>
@@ -3652,13 +3661,13 @@
         <v>206</v>
       </c>
       <c r="H15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J15" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K15">
         <v>114</v>
@@ -3697,7 +3706,7 @@
         <v>24.5</v>
       </c>
       <c r="W15" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X15">
         <v>-0.013333</v>
@@ -3724,12 +3733,12 @@
         <v>27.411763</v>
       </c>
     </row>
-    <row r="16" spans="1:31">
+    <row r="16" spans="1:32">
       <c r="A16" t="s">
         <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C16" s="2">
         <v>45739.29466358796</v>
@@ -3747,13 +3756,13 @@
         <v>210</v>
       </c>
       <c r="H16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J16" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K16">
         <v>111</v>
@@ -3792,7 +3801,7 @@
         <v>24.56666667</v>
       </c>
       <c r="W16" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X16">
         <v>0.002222</v>
@@ -3824,7 +3833,7 @@
         <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C17" s="2">
         <v>45739.29498133102</v>
@@ -3842,13 +3851,13 @@
         <v>240</v>
       </c>
       <c r="H17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J17" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K17">
         <v>118</v>
@@ -3887,7 +3896,7 @@
         <v>24.8</v>
       </c>
       <c r="W17" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X17">
         <v>0.007778</v>
@@ -3919,7 +3928,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C18" s="2">
         <v>45739.29528328704</v>
@@ -3937,13 +3946,13 @@
         <v>266</v>
       </c>
       <c r="H18" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I18" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J18" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K18">
         <v>106</v>
@@ -3982,7 +3991,7 @@
         <v>25.13333333</v>
       </c>
       <c r="W18" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X18">
         <v>0.005556</v>
@@ -4014,7 +4023,7 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C19" s="2">
         <v>45739.29535815972</v>
@@ -4032,13 +4041,13 @@
         <v>270</v>
       </c>
       <c r="H19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I19" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J19" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K19">
         <v>117</v>
@@ -4077,7 +4086,7 @@
         <v>25.63333333</v>
       </c>
       <c r="W19" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X19">
         <v>0.016667</v>
@@ -4109,7 +4118,7 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C20" s="2">
         <v>45739.29566071759</v>
@@ -4127,13 +4136,13 @@
         <v>296</v>
       </c>
       <c r="H20" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I20" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J20" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K20">
         <v>114</v>
@@ -4172,7 +4181,7 @@
         <v>26.36666667</v>
       </c>
       <c r="W20" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X20">
         <v>0.024444</v>
@@ -4204,7 +4213,7 @@
         <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C21" s="2">
         <v>45739.29567648148</v>
@@ -4222,13 +4231,13 @@
         <v>300</v>
       </c>
       <c r="H21" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I21" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J21" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K21">
         <v>109</v>
@@ -4267,7 +4276,7 @@
         <v>26.23333333</v>
       </c>
       <c r="W21" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X21">
         <v>-0.004444</v>
@@ -4299,7 +4308,7 @@
         <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C22" s="2">
         <v>45739.29597946759</v>
@@ -4317,13 +4326,13 @@
         <v>326</v>
       </c>
       <c r="H22" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I22" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J22" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K22">
         <v>115</v>
@@ -4362,7 +4371,7 @@
         <v>25.8</v>
       </c>
       <c r="W22" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X22">
         <v>-0.014444</v>
@@ -4394,7 +4403,7 @@
         <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C23" s="2">
         <v>45739.29605295139</v>
@@ -4412,13 +4421,13 @@
         <v>330</v>
       </c>
       <c r="H23" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I23" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J23" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K23">
         <v>127</v>
@@ -4457,7 +4466,7 @@
         <v>25.96666667</v>
       </c>
       <c r="W23" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X23">
         <v>0.005556</v>
@@ -4489,7 +4498,7 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C24" s="2">
         <v>45739.29634956019</v>
@@ -4507,13 +4516,13 @@
         <v>356</v>
       </c>
       <c r="H24" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I24" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J24" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K24">
         <v>114</v>
@@ -4552,7 +4561,7 @@
         <v>26.86666667</v>
       </c>
       <c r="W24" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X24">
         <v>0.03</v>
@@ -4584,7 +4593,7 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C25" s="2">
         <v>45739.29637664352</v>
@@ -4602,13 +4611,13 @@
         <v>360</v>
       </c>
       <c r="H25" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I25" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J25" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K25">
         <v>122</v>
@@ -4647,7 +4656,7 @@
         <v>26.93333333</v>
       </c>
       <c r="W25" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X25">
         <v>0.002222</v>
@@ -4679,7 +4688,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C26" s="2">
         <v>45739.29666893519</v>
@@ -4697,13 +4706,13 @@
         <v>386</v>
       </c>
       <c r="H26" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I26" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J26" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K26">
         <v>122</v>
@@ -4742,7 +4751,7 @@
         <v>27.36666667</v>
       </c>
       <c r="W26" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X26">
         <v>0.014444</v>
@@ -4774,7 +4783,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C27" s="2">
         <v>45739.29674670139</v>
@@ -4792,13 +4801,13 @@
         <v>390</v>
       </c>
       <c r="H27" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I27" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J27" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K27">
         <v>118</v>
@@ -4837,7 +4846,7 @@
         <v>27.66666667</v>
       </c>
       <c r="W27" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X27">
         <v>0.01</v>
@@ -4869,7 +4878,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C28" s="2">
         <v>45739.29704425926</v>
@@ -4887,13 +4896,13 @@
         <v>416</v>
       </c>
       <c r="H28" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I28" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J28" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K28">
         <v>130</v>
@@ -4932,7 +4941,7 @@
         <v>27.76666667</v>
       </c>
       <c r="W28" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X28">
         <v>0.003333</v>
@@ -4964,7 +4973,7 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C29" s="2">
         <v>45739.29706893519</v>
@@ -4982,13 +4991,13 @@
         <v>420</v>
       </c>
       <c r="H29" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I29" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J29" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K29">
         <v>123</v>
@@ -5027,7 +5036,7 @@
         <v>27.7</v>
       </c>
       <c r="W29" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X29">
         <v>-0.002222</v>
@@ -5059,7 +5068,7 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C30" s="2">
         <v>45739.29736284722</v>
@@ -5077,13 +5086,13 @@
         <v>446</v>
       </c>
       <c r="H30" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I30" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J30" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K30">
         <v>129</v>
@@ -5122,7 +5131,7 @@
         <v>27.43333333</v>
       </c>
       <c r="W30" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X30">
         <v>-0.008888999999999999</v>
@@ -5154,7 +5163,7 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C31" s="2">
         <v>45739.29744186343</v>
@@ -5172,13 +5181,13 @@
         <v>450</v>
       </c>
       <c r="H31" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I31" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J31" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K31">
         <v>128</v>
@@ -5217,7 +5226,7 @@
         <v>26.9</v>
       </c>
       <c r="W31" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X31">
         <v>-0.017778</v>
@@ -5249,7 +5258,7 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C32" s="2">
         <v>45739.29773881944</v>
@@ -5267,13 +5276,13 @@
         <v>476</v>
       </c>
       <c r="H32" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I32" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J32" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K32">
         <v>129</v>
@@ -5312,7 +5321,7 @@
         <v>25.13333333</v>
       </c>
       <c r="W32" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X32">
         <v>-0.058889</v>
@@ -5344,7 +5353,7 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C33" s="2">
         <v>45739.29776020833</v>
@@ -5362,13 +5371,13 @@
         <v>480</v>
       </c>
       <c r="H33" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I33" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J33" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K33">
         <v>132</v>
@@ -5407,7 +5416,7 @@
         <v>25.33333333</v>
       </c>
       <c r="W33" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X33">
         <v>0.006667</v>
@@ -5439,7 +5448,7 @@
         <v>25</v>
       </c>
       <c r="B34" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C34" s="2">
         <v>45739.29805799769</v>
@@ -5457,13 +5466,13 @@
         <v>506</v>
       </c>
       <c r="H34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I34" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J34" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K34">
         <v>130</v>
@@ -5502,7 +5511,7 @@
         <v>26.03333333</v>
       </c>
       <c r="W34" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X34">
         <v>0.023333</v>
@@ -5534,7 +5543,7 @@
         <v>25</v>
       </c>
       <c r="B35" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C35" s="2">
         <v>45739.29813596065</v>
@@ -5552,13 +5561,13 @@
         <v>510</v>
       </c>
       <c r="H35" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I35" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J35" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K35">
         <v>127</v>
@@ -5597,7 +5606,7 @@
         <v>26.03333333</v>
       </c>
       <c r="W35" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X35">
         <v>0</v>
@@ -5629,7 +5638,7 @@
         <v>25</v>
       </c>
       <c r="B36" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C36" s="2">
         <v>45739.29843693287</v>
@@ -5647,13 +5656,13 @@
         <v>536</v>
       </c>
       <c r="H36" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I36" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J36" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K36">
         <v>129</v>
@@ -5692,7 +5701,7 @@
         <v>25.83333333</v>
       </c>
       <c r="W36" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X36">
         <v>-0.006667</v>
@@ -5724,7 +5733,7 @@
         <v>25</v>
       </c>
       <c r="B37" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C37" s="2">
         <v>45739.29845436342</v>
@@ -5742,13 +5751,13 @@
         <v>540</v>
       </c>
       <c r="H37" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I37" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J37" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K37">
         <v>139</v>
@@ -5787,7 +5796,7 @@
         <v>25.76666667</v>
       </c>
       <c r="W37" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X37">
         <v>-0.002222</v>
@@ -5819,7 +5828,7 @@
         <v>25</v>
       </c>
       <c r="B38" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C38" s="2">
         <v>45739.29875199074</v>
@@ -5837,13 +5846,13 @@
         <v>566</v>
       </c>
       <c r="H38" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I38" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J38" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K38">
         <v>130</v>
@@ -5882,7 +5891,7 @@
         <v>25.46666667</v>
       </c>
       <c r="W38" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X38">
         <v>-0.01</v>
@@ -5914,7 +5923,7 @@
         <v>25</v>
       </c>
       <c r="B39" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C39" s="2">
         <v>45739.29883042824</v>
@@ -5932,13 +5941,13 @@
         <v>570</v>
       </c>
       <c r="H39" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I39" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J39" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K39">
         <v>123</v>
@@ -5977,7 +5986,7 @@
         <v>25.56666667</v>
       </c>
       <c r="W39" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X39">
         <v>0.003333</v>
@@ -6009,7 +6018,7 @@
         <v>25</v>
       </c>
       <c r="B40" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C40" s="2">
         <v>45739.29912760416</v>
@@ -6027,13 +6036,13 @@
         <v>596</v>
       </c>
       <c r="H40" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I40" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J40" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K40">
         <v>131</v>
@@ -6072,7 +6081,7 @@
         <v>25.16666667</v>
       </c>
       <c r="W40" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X40">
         <v>-0.013333</v>
@@ -6104,7 +6113,7 @@
         <v>25</v>
       </c>
       <c r="B41" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C41" s="2">
         <v>45739.29914949074</v>
@@ -6122,13 +6131,13 @@
         <v>600</v>
       </c>
       <c r="H41" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I41" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J41" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K41">
         <v>125</v>
@@ -6167,7 +6176,7 @@
         <v>25.06666667</v>
       </c>
       <c r="W41" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X41">
         <v>-0.003333</v>
@@ -6199,7 +6208,7 @@
         <v>25</v>
       </c>
       <c r="B42" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C42" s="2">
         <v>45739.29944946759</v>
@@ -6217,13 +6226,13 @@
         <v>626</v>
       </c>
       <c r="H42" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I42" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J42" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K42">
         <v>130</v>
@@ -6262,7 +6271,7 @@
         <v>25.6</v>
       </c>
       <c r="W42" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X42">
         <v>0.017778</v>
@@ -6294,7 +6303,7 @@
         <v>25</v>
       </c>
       <c r="B43" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C43" s="2">
         <v>45739.2995312963</v>
@@ -6312,13 +6321,13 @@
         <v>630</v>
       </c>
       <c r="H43" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I43" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J43" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K43">
         <v>138</v>
@@ -6357,7 +6366,7 @@
         <v>25.76666667</v>
       </c>
       <c r="W43" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X43">
         <v>0.005556</v>
@@ -6389,7 +6398,7 @@
         <v>25</v>
       </c>
       <c r="B44" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C44" s="2">
         <v>45739.29982260417</v>
@@ -6407,13 +6416,13 @@
         <v>656</v>
       </c>
       <c r="H44" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I44" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J44" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K44">
         <v>129</v>
@@ -6452,7 +6461,7 @@
         <v>25.43333333</v>
       </c>
       <c r="W44" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X44">
         <v>-0.011111</v>
@@ -6484,7 +6493,7 @@
         <v>25</v>
       </c>
       <c r="B45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C45" s="2">
         <v>45739.29984265046</v>
@@ -6502,13 +6511,13 @@
         <v>660</v>
       </c>
       <c r="H45" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I45" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J45" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K45">
         <v>122</v>
@@ -6547,7 +6556,7 @@
         <v>24.9</v>
       </c>
       <c r="W45" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X45">
         <v>-0.017778</v>
@@ -6579,7 +6588,7 @@
         <v>25</v>
       </c>
       <c r="B46" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C46" s="2">
         <v>45739.30014135416</v>
@@ -6597,13 +6606,13 @@
         <v>686</v>
       </c>
       <c r="H46" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I46" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J46" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K46">
         <v>133</v>
@@ -6642,7 +6651,7 @@
         <v>24.53333333</v>
       </c>
       <c r="W46" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X46">
         <v>-0.012222</v>
@@ -6674,7 +6683,7 @@
         <v>25</v>
       </c>
       <c r="B47" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C47" s="2">
         <v>45739.30021931713</v>
@@ -6692,13 +6701,13 @@
         <v>690</v>
       </c>
       <c r="H47" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I47" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J47" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K47">
         <v>135</v>
@@ -6737,7 +6746,7 @@
         <v>24.6</v>
       </c>
       <c r="W47" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X47">
         <v>0.002222</v>
@@ -6769,7 +6778,7 @@
         <v>25</v>
       </c>
       <c r="B48" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C48" s="2">
         <v>45739.30051747686</v>
@@ -6787,13 +6796,13 @@
         <v>716</v>
       </c>
       <c r="H48" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I48" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J48" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K48">
         <v>124</v>
@@ -6832,7 +6841,7 @@
         <v>25.06666667</v>
       </c>
       <c r="W48" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X48">
         <v>0.015556</v>
@@ -6864,7 +6873,7 @@
         <v>25</v>
       </c>
       <c r="B49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C49" s="2">
         <v>45739.30053751158</v>
@@ -6882,13 +6891,13 @@
         <v>720</v>
       </c>
       <c r="H49" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I49" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J49" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K49">
         <v>129</v>
@@ -6927,7 +6936,7 @@
         <v>25.4</v>
       </c>
       <c r="W49" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X49">
         <v>0.011111</v>
@@ -6959,7 +6968,7 @@
         <v>25</v>
       </c>
       <c r="B50" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C50" s="2">
         <v>45739.30083628472</v>
@@ -6977,13 +6986,13 @@
         <v>746</v>
       </c>
       <c r="H50" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I50" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J50" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K50">
         <v>117</v>
@@ -7022,7 +7031,7 @@
         <v>25.46666667</v>
       </c>
       <c r="W50" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X50">
         <v>0.002222</v>
@@ -7054,7 +7063,7 @@
         <v>25</v>
       </c>
       <c r="B51" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C51" s="2">
         <v>45739.30093151621</v>
@@ -7072,13 +7081,13 @@
         <v>750</v>
       </c>
       <c r="H51" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I51" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J51" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K51">
         <v>121</v>
@@ -7117,7 +7126,7 @@
         <v>25.66666667</v>
       </c>
       <c r="W51" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X51">
         <v>0.006667</v>
@@ -7149,7 +7158,7 @@
         <v>25</v>
       </c>
       <c r="B52" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C52" s="2">
         <v>45739.30121231481</v>
@@ -7167,13 +7176,13 @@
         <v>776</v>
       </c>
       <c r="H52" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I52" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J52" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K52">
         <v>124</v>
@@ -7212,7 +7221,7 @@
         <v>25.63333333</v>
       </c>
       <c r="W52" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X52">
         <v>-0.001111</v>
@@ -7244,7 +7253,7 @@
         <v>25</v>
       </c>
       <c r="B53" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C53" s="2">
         <v>45739.30123253472</v>
@@ -7262,13 +7271,13 @@
         <v>780</v>
       </c>
       <c r="H53" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I53" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J53" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K53">
         <v>122</v>
@@ -7307,7 +7316,7 @@
         <v>25.16666667</v>
       </c>
       <c r="W53" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X53">
         <v>-0.015556</v>
@@ -7339,7 +7348,7 @@
         <v>25</v>
       </c>
       <c r="B54" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C54" s="2">
         <v>45739.30153113426</v>
@@ -7357,13 +7366,13 @@
         <v>806</v>
       </c>
       <c r="H54" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I54" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J54" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K54">
         <v>110</v>
@@ -7402,7 +7411,7 @@
         <v>26.03333333</v>
       </c>
       <c r="W54" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X54">
         <v>0.028889</v>
@@ -7434,7 +7443,7 @@
         <v>25</v>
       </c>
       <c r="B55" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C55" s="2">
         <v>45739.30190840278</v>
@@ -7452,13 +7461,13 @@
         <v>836</v>
       </c>
       <c r="H55" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I55" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J55" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K55">
         <v>111</v>
@@ -7497,7 +7506,7 @@
         <v>26.23333333</v>
       </c>
       <c r="W55" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X55">
         <v>0.006667</v>
@@ -7529,7 +7538,7 @@
         <v>25</v>
       </c>
       <c r="B56" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C56" s="2">
         <v>45739.30222625</v>
@@ -7547,13 +7556,13 @@
         <v>866</v>
       </c>
       <c r="H56" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J56" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K56">
         <v>111</v>
@@ -7592,7 +7601,7 @@
         <v>26.33333333</v>
       </c>
       <c r="W56" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X56">
         <v>0.003333</v>
@@ -7624,7 +7633,7 @@
         <v>25</v>
       </c>
       <c r="B57" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C57" s="2">
         <v>45739.30292140046</v>
@@ -7642,13 +7651,13 @@
         <v>926</v>
       </c>
       <c r="H57" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I57" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J57" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K57">
         <v>105</v>
@@ -7687,7 +7696,7 @@
         <v>28.96666667</v>
       </c>
       <c r="W57" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X57">
         <v>0.043889</v>
@@ -7719,7 +7728,7 @@
         <v>25</v>
       </c>
       <c r="B58" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C58" s="2">
         <v>45739.30329885417</v>
@@ -7737,13 +7746,13 @@
         <v>956</v>
       </c>
       <c r="H58" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I58" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J58" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K58">
         <v>100</v>
@@ -7782,7 +7791,7 @@
         <v>26.53333333</v>
       </c>
       <c r="W58" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X58">
         <v>-0.081111</v>
@@ -7814,7 +7823,7 @@
         <v>25</v>
       </c>
       <c r="B59" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C59" s="2">
         <v>45739.30361577546</v>
@@ -7832,13 +7841,13 @@
         <v>986</v>
       </c>
       <c r="H59" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I59" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J59" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K59">
         <v>103</v>
@@ -7877,7 +7886,7 @@
         <v>26.86666667</v>
       </c>
       <c r="W59" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X59">
         <v>0.011111</v>
@@ -7909,7 +7918,7 @@
         <v>25</v>
       </c>
       <c r="B60" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C60" s="2">
         <v>45739.30399247685</v>
@@ -7927,13 +7936,13 @@
         <v>1016</v>
       </c>
       <c r="H60" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I60" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J60" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K60">
         <v>102</v>
@@ -7972,7 +7981,7 @@
         <v>27.63333333</v>
       </c>
       <c r="W60" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X60">
         <v>0.025556</v>
@@ -8004,7 +8013,7 @@
         <v>25</v>
       </c>
       <c r="B61" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C61" s="2">
         <v>45739.30431127315</v>
@@ -8022,13 +8031,13 @@
         <v>1046</v>
       </c>
       <c r="H61" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I61" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J61" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K61">
         <v>101</v>
@@ -8067,7 +8076,7 @@
         <v>27</v>
       </c>
       <c r="W61" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X61">
         <v>-0.021111</v>
@@ -8099,7 +8108,7 @@
         <v>25</v>
       </c>
       <c r="B62" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C62" s="2">
         <v>45739.30468756944</v>
@@ -8117,13 +8126,13 @@
         <v>1076</v>
       </c>
       <c r="H62" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I62" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J62" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K62">
         <v>94</v>
@@ -8162,7 +8171,7 @@
         <v>27.76666667</v>
       </c>
       <c r="W62" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X62">
         <v>0.025556</v>
@@ -8194,7 +8203,7 @@
         <v>25</v>
       </c>
       <c r="B63" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C63" s="2">
         <v>45739.30538244213</v>
@@ -8212,13 +8221,13 @@
         <v>1136</v>
       </c>
       <c r="H63" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I63" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J63" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K63">
         <v>97</v>
@@ -8257,7 +8266,7 @@
         <v>27.11666667</v>
       </c>
       <c r="W63" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X63">
         <v>-0.010833</v>
@@ -8289,7 +8298,7 @@
         <v>25</v>
       </c>
       <c r="B64" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C64" s="2">
         <v>45739.30569984954</v>
@@ -8307,13 +8316,13 @@
         <v>1166</v>
       </c>
       <c r="H64" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I64" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J64" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K64">
         <v>96</v>
@@ -8352,7 +8361,7 @@
         <v>26.8</v>
       </c>
       <c r="W64" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X64">
         <v>-0.010556</v>
@@ -8384,7 +8393,7 @@
         <v>25</v>
       </c>
       <c r="B65" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C65" s="2">
         <v>45739.30607695602</v>
@@ -8402,13 +8411,13 @@
         <v>1196</v>
       </c>
       <c r="H65" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I65" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J65" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K65">
         <v>94</v>
@@ -8447,7 +8456,7 @@
         <v>28.63333333</v>
       </c>
       <c r="W65" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X65">
         <v>0.061111</v>
@@ -8479,7 +8488,7 @@
         <v>25</v>
       </c>
       <c r="B66" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C66" s="2">
         <v>45739.306394375</v>
@@ -8497,13 +8506,13 @@
         <v>1226</v>
       </c>
       <c r="H66" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I66" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J66" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K66">
         <v>97</v>
@@ -8542,7 +8551,7 @@
         <v>26.03333333</v>
       </c>
       <c r="W66" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X66">
         <v>-0.08666699999999999</v>
@@ -8574,7 +8583,7 @@
         <v>25</v>
       </c>
       <c r="B67" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C67" s="2">
         <v>45739.30677082176</v>
@@ -8592,13 +8601,13 @@
         <v>1256</v>
       </c>
       <c r="H67" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I67" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J67" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K67">
         <v>106</v>
@@ -8637,7 +8646,7 @@
         <v>30.03333333</v>
       </c>
       <c r="W67" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X67">
         <v>0.133333</v>
@@ -8669,7 +8678,7 @@
         <v>25</v>
       </c>
       <c r="B68" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C68" s="2">
         <v>45739.30708983797</v>
@@ -8687,13 +8696,13 @@
         <v>1286</v>
       </c>
       <c r="H68" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I68" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J68" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K68">
         <v>116</v>
@@ -8732,7 +8741,7 @@
         <v>29.36666667</v>
       </c>
       <c r="W68" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X68">
         <v>-0.022222</v>
@@ -8764,7 +8773,7 @@
         <v>25</v>
       </c>
       <c r="B69" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C69" s="2">
         <v>45739.30746571759</v>
@@ -8782,13 +8791,13 @@
         <v>1316</v>
       </c>
       <c r="H69" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I69" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J69" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K69">
         <v>102</v>
@@ -8827,7 +8836,7 @@
         <v>29.36666667</v>
       </c>
       <c r="W69" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X69">
         <v>0</v>
@@ -8859,7 +8868,7 @@
         <v>25</v>
       </c>
       <c r="B70" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C70" s="2">
         <v>45739.30778394676</v>
@@ -8877,13 +8886,13 @@
         <v>1346</v>
       </c>
       <c r="H70" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I70" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J70" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K70">
         <v>103</v>
@@ -8922,7 +8931,7 @@
         <v>29.73333333</v>
       </c>
       <c r="W70" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X70">
         <v>0.012222</v>
@@ -8954,7 +8963,7 @@
         <v>25</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C71" s="2">
         <v>45739.3081615162</v>
@@ -8972,13 +8981,13 @@
         <v>1376</v>
       </c>
       <c r="H71" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I71" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J71" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K71">
         <v>107</v>
@@ -9017,7 +9026,7 @@
         <v>29.7</v>
       </c>
       <c r="W71" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X71">
         <v>-0.001111</v>
@@ -9049,7 +9058,7 @@
         <v>25</v>
       </c>
       <c r="B72" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C72" s="2">
         <v>45739.30847909722</v>
@@ -9067,13 +9076,13 @@
         <v>1406</v>
       </c>
       <c r="H72" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I72" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J72" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K72">
         <v>115</v>
@@ -9112,7 +9121,7 @@
         <v>30.5</v>
       </c>
       <c r="W72" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X72">
         <v>0.026667</v>
@@ -9144,7 +9153,7 @@
         <v>25</v>
       </c>
       <c r="B73" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C73" s="2">
         <v>45739.30885538195</v>
@@ -9162,13 +9171,13 @@
         <v>1436</v>
       </c>
       <c r="H73" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I73" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J73" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K73">
         <v>111</v>
@@ -9207,7 +9216,7 @@
         <v>30.96666667</v>
       </c>
       <c r="W73" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X73">
         <v>0.015556</v>
@@ -9239,7 +9248,7 @@
         <v>25</v>
       </c>
       <c r="B74" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C74" s="2">
         <v>45739.3095443287</v>
@@ -9257,13 +9266,13 @@
         <v>1496</v>
       </c>
       <c r="H74" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I74" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J74" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K74">
         <v>127</v>
@@ -9302,7 +9311,7 @@
         <v>31</v>
       </c>
       <c r="W74" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X74">
         <v>0.000556</v>
@@ -9334,7 +9343,7 @@
         <v>25</v>
       </c>
       <c r="B75" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C75" s="2">
         <v>45739.30986297454</v>
@@ -9352,13 +9361,13 @@
         <v>1526</v>
       </c>
       <c r="H75" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I75" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J75" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K75">
         <v>122</v>
@@ -9397,7 +9406,7 @@
         <v>29.83333333</v>
       </c>
       <c r="W75" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X75">
         <v>-0.038889</v>
@@ -9429,7 +9438,7 @@
         <v>25</v>
       </c>
       <c r="B76" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C76" s="2">
         <v>45739.31023907408</v>
@@ -9447,13 +9456,13 @@
         <v>1556</v>
       </c>
       <c r="H76" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I76" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J76" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K76">
         <v>127</v>
@@ -9492,7 +9501,7 @@
         <v>27.46666667</v>
       </c>
       <c r="W76" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X76">
         <v>-0.078889</v>
@@ -9524,7 +9533,7 @@
         <v>25</v>
       </c>
       <c r="B77" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C77" s="2">
         <v>45739.3105570949</v>
@@ -9542,13 +9551,13 @@
         <v>1586</v>
       </c>
       <c r="H77" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I77" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J77" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K77">
         <v>126</v>
@@ -9587,7 +9596,7 @@
         <v>20.7</v>
       </c>
       <c r="W77" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X77">
         <v>-0.225556</v>
@@ -9619,7 +9628,7 @@
         <v>25</v>
       </c>
       <c r="B78" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C78" s="2">
         <v>45739.31093354167</v>
@@ -9637,13 +9646,13 @@
         <v>1616</v>
       </c>
       <c r="H78" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I78" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J78" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K78">
         <v>128</v>
@@ -9682,7 +9691,7 @@
         <v>27.86666667</v>
       </c>
       <c r="W78" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X78">
         <v>0.238889</v>
@@ -9714,7 +9723,7 @@
         <v>25</v>
       </c>
       <c r="B79" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C79" s="2">
         <v>45739.31162853009</v>
@@ -9732,13 +9741,13 @@
         <v>1676</v>
       </c>
       <c r="H79" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I79" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J79" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K79">
         <v>71</v>
@@ -9777,7 +9786,7 @@
         <v>29.05</v>
       </c>
       <c r="W79" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X79">
         <v>0.019722</v>
@@ -9809,7 +9818,7 @@
         <v>25</v>
       </c>
       <c r="B80" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C80" s="2">
         <v>45739.31194724537</v>
@@ -9827,13 +9836,13 @@
         <v>1706</v>
       </c>
       <c r="H80" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I80" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J80" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K80">
         <v>70</v>
@@ -9872,7 +9881,7 @@
         <v>32.86666667</v>
       </c>
       <c r="W80" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X80">
         <v>0.127222</v>
@@ -9899,12 +9908,12 @@
         <v>28.727091</v>
       </c>
     </row>
-    <row r="81" spans="1:31">
+    <row r="81" spans="1:32">
       <c r="A81" t="s">
         <v>25</v>
       </c>
       <c r="B81" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C81" s="2">
         <v>45739.31232280093</v>
@@ -9922,13 +9931,13 @@
         <v>1736</v>
       </c>
       <c r="H81" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I81" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J81" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K81">
         <v>54</v>
@@ -9967,7 +9976,7 @@
         <v>34.56666667</v>
       </c>
       <c r="W81" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X81">
         <v>0.056667</v>
@@ -9994,12 +10003,12 @@
         <v>28.108142</v>
       </c>
     </row>
-    <row r="82" spans="1:31">
+    <row r="82" spans="1:32">
       <c r="A82" t="s">
         <v>25</v>
       </c>
       <c r="B82" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C82" s="2">
         <v>45739.312641875</v>
@@ -10017,13 +10026,13 @@
         <v>1766</v>
       </c>
       <c r="H82" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I82" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J82" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K82">
         <v>81</v>
@@ -10062,7 +10071,7 @@
         <v>30.03333333</v>
       </c>
       <c r="W82" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X82">
         <v>-0.151111</v>
@@ -10089,12 +10098,12 @@
         <v>27.519948</v>
       </c>
     </row>
-    <row r="83" spans="1:31">
+    <row r="83" spans="1:32">
       <c r="A83" t="s">
         <v>25</v>
       </c>
       <c r="B83" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C83" s="2">
         <v>45739.31301729166</v>
@@ -10112,13 +10121,13 @@
         <v>1796</v>
       </c>
       <c r="H83" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I83" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J83" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K83">
         <v>71</v>
@@ -10157,7 +10166,7 @@
         <v>29.86666667</v>
       </c>
       <c r="W83" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X83">
         <v>-0.005556</v>
@@ -10184,12 +10193,12 @@
         <v>26.898216</v>
       </c>
     </row>
-    <row r="84" spans="1:31">
+    <row r="84" spans="1:32">
       <c r="A84" t="s">
         <v>25</v>
       </c>
       <c r="B84" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C84" s="2">
         <v>45739.3133352662</v>
@@ -10207,13 +10216,13 @@
         <v>1826</v>
       </c>
       <c r="H84" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I84" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J84" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K84">
         <v>108</v>
@@ -10252,7 +10261,7 @@
         <v>25.4</v>
       </c>
       <c r="W84" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X84">
         <v>-0.148889</v>
@@ -10279,12 +10288,12 @@
         <v>26.347693</v>
       </c>
     </row>
-    <row r="85" spans="1:31">
+    <row r="85" spans="1:32">
       <c r="A85" t="s">
         <v>25</v>
       </c>
       <c r="B85" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C85" s="2">
         <v>45739.31371130787</v>
@@ -10302,13 +10311,13 @@
         <v>1856</v>
       </c>
       <c r="H85" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I85" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J85" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K85">
         <v>109</v>
@@ -10347,7 +10356,7 @@
         <v>31.56666667</v>
       </c>
       <c r="W85" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X85">
         <v>0.205556</v>
@@ -10374,12 +10383,12 @@
         <v>25.644959</v>
       </c>
     </row>
-    <row r="86" spans="1:31">
+    <row r="86" spans="1:32">
       <c r="A86" t="s">
         <v>25</v>
       </c>
       <c r="B86" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C86" s="2">
         <v>45739.31403149306</v>
@@ -10397,13 +10406,13 @@
         <v>1886</v>
       </c>
       <c r="H86" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I86" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J86" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K86">
         <v>106</v>
@@ -10442,7 +10451,7 @@
         <v>19.43333333</v>
       </c>
       <c r="W86" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X86">
         <v>-0.404444</v>
@@ -10469,12 +10478,12 @@
         <v>25.206592</v>
       </c>
     </row>
-    <row r="87" spans="1:31">
+    <row r="87" spans="1:32">
       <c r="A87" t="s">
         <v>25</v>
       </c>
       <c r="B87" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C87" s="2">
         <v>45739.31440606481</v>
@@ -10492,13 +10501,13 @@
         <v>1916</v>
       </c>
       <c r="H87" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I87" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J87" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K87">
         <v>140</v>
@@ -10537,7 +10546,7 @@
         <v>30.4</v>
       </c>
       <c r="W87" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X87">
         <v>0.365556</v>
@@ -10564,12 +10573,12 @@
         <v>24.519166</v>
       </c>
     </row>
-    <row r="88" spans="1:31">
+    <row r="88" spans="1:32">
       <c r="A88" t="s">
         <v>25</v>
       </c>
       <c r="B88" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C88" s="2">
         <v>45739.31472450231</v>
@@ -10587,13 +10596,13 @@
         <v>1946</v>
       </c>
       <c r="H88" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I88" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J88" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K88">
         <v>132</v>
@@ -10632,7 +10641,7 @@
         <v>17.86666667</v>
       </c>
       <c r="W88" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X88">
         <v>-0.417778</v>
@@ -10659,12 +10668,12 @@
         <v>24.117431</v>
       </c>
     </row>
-    <row r="89" spans="1:31">
+    <row r="89" spans="1:32">
       <c r="A89" t="s">
         <v>25</v>
       </c>
       <c r="B89" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C89" s="2">
         <v>45739.31510199074</v>
@@ -10682,13 +10691,13 @@
         <v>1976</v>
       </c>
       <c r="H89" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I89" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J89" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K89">
         <v>130</v>
@@ -10727,7 +10736,7 @@
         <v>21</v>
       </c>
       <c r="W89" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X89">
         <v>0.104444</v>
@@ -10754,12 +10763,12 @@
         <v>23.65039</v>
       </c>
     </row>
-    <row r="90" spans="1:31">
+    <row r="90" spans="1:32">
       <c r="A90" t="s">
         <v>25</v>
       </c>
       <c r="B90" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C90" s="2">
         <v>45739.31541944444</v>
@@ -10777,13 +10786,13 @@
         <v>2006</v>
       </c>
       <c r="H90" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I90" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J90" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K90">
         <v>135</v>
@@ -10822,7 +10831,7 @@
         <v>23.96666667</v>
       </c>
       <c r="W90" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X90">
         <v>0.098889</v>
@@ -10849,12 +10858,12 @@
         <v>23.127539</v>
       </c>
     </row>
-    <row r="91" spans="1:31">
+    <row r="91" spans="1:32">
       <c r="A91" t="s">
         <v>25</v>
       </c>
       <c r="B91" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C91" s="2">
         <v>45739.31579568287</v>
@@ -10872,13 +10881,13 @@
         <v>2036</v>
       </c>
       <c r="H91" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I91" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J91" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K91">
         <v>138</v>
@@ -10917,7 +10926,7 @@
         <v>22.4</v>
       </c>
       <c r="W91" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X91">
         <v>-0.052222</v>
@@ -10944,12 +10953,12 @@
         <v>22.65193</v>
       </c>
     </row>
-    <row r="92" spans="1:31">
+    <row r="92" spans="1:32">
       <c r="A92" t="s">
         <v>25</v>
       </c>
       <c r="B92" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C92" s="2">
         <v>45739.31611710648</v>
@@ -10967,13 +10976,13 @@
         <v>2066</v>
       </c>
       <c r="H92" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I92" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J92" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K92">
         <v>124</v>
@@ -11012,7 +11021,7 @@
         <v>26.83333333</v>
       </c>
       <c r="W92" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="X92">
         <v>0.147778</v>
@@ -11039,12 +11048,12 @@
         <v>22.102953</v>
       </c>
     </row>
-    <row r="93" spans="1:31">
+    <row r="93" spans="1:32">
       <c r="A93" t="s">
         <v>25</v>
       </c>
       <c r="B93" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C93" s="2">
         <v>45739.31649013889</v>
@@ -11062,13 +11071,13 @@
         <v>2096</v>
       </c>
       <c r="H93" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I93" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J93" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K93">
         <v>146</v>
@@ -11107,7 +11116,7 @@
         <v>26.3</v>
       </c>
       <c r="W93" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X93">
         <v>-0.017778</v>
@@ -11133,13 +11142,16 @@
       <c r="AE93">
         <v>21.590928</v>
       </c>
+      <c r="AF93" t="s">
+        <v>394</v>
+      </c>
     </row>
-    <row r="94" spans="1:31">
+    <row r="94" spans="1:32">
       <c r="A94" t="s">
         <v>25</v>
       </c>
       <c r="B94" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C94" s="2">
         <v>45739.31680828704</v>
@@ -11157,13 +11169,13 @@
         <v>2126</v>
       </c>
       <c r="H94" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I94" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J94" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K94">
         <v>128</v>
@@ -11202,7 +11214,7 @@
         <v>17.93333333</v>
       </c>
       <c r="W94" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X94">
         <v>-0.278889</v>
@@ -11229,12 +11241,12 @@
         <v>21.258515</v>
       </c>
     </row>
-    <row r="95" spans="1:31">
+    <row r="95" spans="1:32">
       <c r="A95" t="s">
         <v>25</v>
       </c>
       <c r="B95" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C95" s="2">
         <v>45739.31718446759</v>
@@ -11252,13 +11264,13 @@
         <v>2156</v>
       </c>
       <c r="H95" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I95" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J95" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K95">
         <v>137</v>
@@ -11297,7 +11309,7 @@
         <v>18.3</v>
       </c>
       <c r="W95" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X95">
         <v>0.012222</v>
@@ -11324,12 +11336,12 @@
         <v>20.934547</v>
       </c>
     </row>
-    <row r="96" spans="1:31">
+    <row r="96" spans="1:32">
       <c r="A96" t="s">
         <v>25</v>
       </c>
       <c r="B96" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C96" s="2">
         <v>45739.3175028125</v>
@@ -11347,13 +11359,13 @@
         <v>2186</v>
       </c>
       <c r="H96" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I96" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J96" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K96">
         <v>149</v>
@@ -11392,7 +11404,7 @@
         <v>18.53333333</v>
       </c>
       <c r="W96" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X96">
         <v>0.007778</v>
@@ -11424,7 +11436,7 @@
         <v>25</v>
       </c>
       <c r="B97" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C97" s="2">
         <v>45739.31787883102</v>
@@ -11442,13 +11454,13 @@
         <v>2216</v>
       </c>
       <c r="H97" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I97" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J97" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K97">
         <v>165</v>
@@ -11487,7 +11499,7 @@
         <v>17.2</v>
       </c>
       <c r="W97" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X97">
         <v>-0.044444</v>
@@ -11519,7 +11531,7 @@
         <v>25</v>
       </c>
       <c r="B98" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C98" s="2">
         <v>45739.31819840278</v>
@@ -11537,13 +11549,13 @@
         <v>2246</v>
       </c>
       <c r="H98" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I98" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J98" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K98">
         <v>120</v>
@@ -11582,7 +11594,7 @@
         <v>17.26666667</v>
       </c>
       <c r="W98" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X98">
         <v>0.002222</v>
@@ -11614,7 +11626,7 @@
         <v>25</v>
       </c>
       <c r="B99" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C99" s="2">
         <v>45739.31857342592</v>
@@ -11632,13 +11644,13 @@
         <v>2276</v>
       </c>
       <c r="H99" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I99" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J99" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K99">
         <v>286</v>
@@ -11677,7 +11689,7 @@
         <v>21.1</v>
       </c>
       <c r="W99" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X99">
         <v>0.127778</v>
@@ -11709,7 +11721,7 @@
         <v>25</v>
       </c>
       <c r="B100" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C100" s="2">
         <v>45739.31889232639</v>
@@ -11727,13 +11739,13 @@
         <v>2306</v>
       </c>
       <c r="H100" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I100" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J100" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K100">
         <v>39</v>
@@ -11772,7 +11784,7 @@
         <v>18.86666667</v>
       </c>
       <c r="W100" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X100">
         <v>-0.074444</v>
@@ -11804,7 +11816,7 @@
         <v>25</v>
       </c>
       <c r="B101" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C101" s="2">
         <v>45739.31926827546</v>
@@ -11822,13 +11834,13 @@
         <v>2336</v>
       </c>
       <c r="H101" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I101" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J101" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K101">
         <v>67</v>
@@ -11867,7 +11879,7 @@
         <v>18.3</v>
       </c>
       <c r="W101" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X101">
         <v>-0.018889</v>
@@ -11899,7 +11911,7 @@
         <v>25</v>
       </c>
       <c r="B102" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C102" s="2">
         <v>45739.31958732639</v>
@@ -11917,13 +11929,13 @@
         <v>2366</v>
       </c>
       <c r="H102" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I102" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J102" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K102">
         <v>107</v>
@@ -11962,7 +11974,7 @@
         <v>18.66666667</v>
       </c>
       <c r="W102" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X102">
         <v>0.012222</v>
@@ -11994,7 +12006,7 @@
         <v>25</v>
       </c>
       <c r="B103" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C103" s="2">
         <v>45739.31996393519</v>
@@ -12012,13 +12024,13 @@
         <v>2396</v>
       </c>
       <c r="H103" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I103" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J103" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K103">
         <v>143</v>
@@ -12057,7 +12069,7 @@
         <v>19</v>
       </c>
       <c r="W103" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X103">
         <v>0.011111</v>
@@ -12089,7 +12101,7 @@
         <v>25</v>
       </c>
       <c r="B104" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C104" s="2">
         <v>45739.32028194444</v>
@@ -12107,13 +12119,13 @@
         <v>2426</v>
       </c>
       <c r="H104" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I104" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J104" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="K104">
         <v>174</v>
@@ -12152,7 +12164,7 @@
         <v>17.93333333</v>
       </c>
       <c r="W104" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X104">
         <v>-0.035556</v>
@@ -12184,7 +12196,7 @@
         <v>25</v>
       </c>
       <c r="B105" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C105" s="2">
         <v>45739.32065820602</v>
@@ -12202,13 +12214,13 @@
         <v>2456</v>
       </c>
       <c r="H105" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I105" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J105" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K105">
         <v>198</v>
@@ -12247,7 +12259,7 @@
         <v>20.66666667</v>
       </c>
       <c r="W105" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X105">
         <v>0.091111</v>
@@ -12279,7 +12291,7 @@
         <v>25</v>
       </c>
       <c r="B106" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C106" s="2">
         <v>45739.32097855324</v>
@@ -12297,13 +12309,13 @@
         <v>2486</v>
       </c>
       <c r="H106" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I106" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J106" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K106">
         <v>191</v>
@@ -12342,7 +12354,7 @@
         <v>19.16666667</v>
       </c>
       <c r="W106" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X106">
         <v>-0.05</v>
@@ -12374,7 +12386,7 @@
         <v>25</v>
       </c>
       <c r="B107" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C107" s="2">
         <v>45739.32135461806</v>
@@ -12392,13 +12404,13 @@
         <v>2516</v>
       </c>
       <c r="H107" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I107" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="J107" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K107">
         <v>160</v>
@@ -12437,7 +12449,7 @@
         <v>18.93333333</v>
       </c>
       <c r="W107" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X107">
         <v>-0.007778</v>
@@ -12469,7 +12481,7 @@
         <v>25</v>
       </c>
       <c r="B108" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C108" s="2">
         <v>45739.32166804398</v>
@@ -12487,13 +12499,13 @@
         <v>2546</v>
       </c>
       <c r="H108" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I108" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J108" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K108">
         <v>196</v>
@@ -12532,7 +12544,7 @@
         <v>18.86666667</v>
       </c>
       <c r="W108" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X108">
         <v>-0.002222</v>
@@ -12564,7 +12576,7 @@
         <v>25</v>
       </c>
       <c r="B109" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C109" s="2">
         <v>45739.32204493056</v>
@@ -12582,13 +12594,13 @@
         <v>2576</v>
       </c>
       <c r="H109" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I109" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J109" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K109">
         <v>191</v>
@@ -12627,7 +12639,7 @@
         <v>18.5</v>
       </c>
       <c r="W109" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X109">
         <v>-0.012222</v>
@@ -12659,7 +12671,7 @@
         <v>25</v>
       </c>
       <c r="B110" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C110" s="2">
         <v>45739.32236390046</v>
@@ -12677,13 +12689,13 @@
         <v>2606</v>
       </c>
       <c r="H110" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I110" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J110" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K110">
         <v>190</v>
@@ -12722,7 +12734,7 @@
         <v>17.3</v>
       </c>
       <c r="W110" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X110">
         <v>-0.04</v>
@@ -12754,7 +12766,7 @@
         <v>25</v>
       </c>
       <c r="B111" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C111" s="2">
         <v>45739.32273914352</v>
@@ -12772,13 +12784,13 @@
         <v>2636</v>
       </c>
       <c r="H111" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I111" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J111" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K111">
         <v>197</v>
@@ -12817,7 +12829,7 @@
         <v>17.53333333</v>
       </c>
       <c r="W111" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X111">
         <v>0.007778</v>
@@ -12849,7 +12861,7 @@
         <v>25</v>
       </c>
       <c r="B112" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C112" s="2">
         <v>45739.32306115741</v>
@@ -12867,13 +12879,13 @@
         <v>2666</v>
       </c>
       <c r="H112" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I112" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J112" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K112">
         <v>220</v>
@@ -12912,7 +12924,7 @@
         <v>18.36666667</v>
       </c>
       <c r="W112" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X112">
         <v>0.027778</v>
@@ -12944,7 +12956,7 @@
         <v>25</v>
       </c>
       <c r="B113" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C113" s="2">
         <v>45739.32343505787</v>
@@ -12962,13 +12974,13 @@
         <v>2696</v>
       </c>
       <c r="H113" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I113" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J113" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K113">
         <v>238</v>
@@ -13007,7 +13019,7 @@
         <v>18.6</v>
       </c>
       <c r="W113" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X113">
         <v>0.007778</v>
@@ -13039,7 +13051,7 @@
         <v>25</v>
       </c>
       <c r="B114" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C114" s="2">
         <v>45739.32375425926</v>
@@ -13057,13 +13069,13 @@
         <v>2726</v>
       </c>
       <c r="H114" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I114" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J114" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K114">
         <v>209</v>
@@ -13102,7 +13114,7 @@
         <v>19.56666667</v>
       </c>
       <c r="W114" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X114">
         <v>0.032222</v>
@@ -13134,7 +13146,7 @@
         <v>25</v>
       </c>
       <c r="B115" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C115" s="2">
         <v>45739.32413025463</v>
@@ -13152,13 +13164,13 @@
         <v>2756</v>
       </c>
       <c r="H115" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I115" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J115" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K115">
         <v>218</v>
@@ -13197,7 +13209,7 @@
         <v>19.93333333</v>
       </c>
       <c r="W115" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X115">
         <v>0.012222</v>
@@ -13229,7 +13241,7 @@
         <v>25</v>
       </c>
       <c r="B116" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C116" s="2">
         <v>45739.32444827546</v>
@@ -13247,13 +13259,13 @@
         <v>2786</v>
       </c>
       <c r="H116" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I116" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J116" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K116">
         <v>231</v>
@@ -13292,7 +13304,7 @@
         <v>18.86666667</v>
       </c>
       <c r="W116" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X116">
         <v>-0.035556</v>
@@ -13324,7 +13336,7 @@
         <v>25</v>
       </c>
       <c r="B117" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C117" s="2">
         <v>45739.32482436342</v>
@@ -13342,13 +13354,13 @@
         <v>2816</v>
       </c>
       <c r="H117" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I117" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J117" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K117">
         <v>227</v>
@@ -13387,7 +13399,7 @@
         <v>18.76666667</v>
       </c>
       <c r="W117" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X117">
         <v>-0.003333</v>
@@ -13419,7 +13431,7 @@
         <v>25</v>
       </c>
       <c r="B118" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C118" s="2">
         <v>45739.3251428588</v>
@@ -13437,13 +13449,13 @@
         <v>2846</v>
       </c>
       <c r="H118" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I118" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J118" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K118">
         <v>236</v>
@@ -13482,7 +13494,7 @@
         <v>18.13333333</v>
       </c>
       <c r="W118" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X118">
         <v>-0.021111</v>
@@ -13514,7 +13526,7 @@
         <v>25</v>
       </c>
       <c r="B119" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C119" s="2">
         <v>45739.32551894676</v>
@@ -13532,13 +13544,13 @@
         <v>2876</v>
       </c>
       <c r="H119" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I119" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J119" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K119">
         <v>243</v>
@@ -13577,7 +13589,7 @@
         <v>18.8</v>
       </c>
       <c r="W119" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X119">
         <v>0.022222</v>
@@ -13609,7 +13621,7 @@
         <v>25</v>
       </c>
       <c r="B120" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C120" s="2">
         <v>45739.32621324074</v>
@@ -13627,13 +13639,13 @@
         <v>2936</v>
       </c>
       <c r="H120" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I120" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J120" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K120">
         <v>267</v>
@@ -13672,7 +13684,7 @@
         <v>18.3</v>
       </c>
       <c r="W120" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X120">
         <v>-0.008333</v>
@@ -13704,7 +13716,7 @@
         <v>25</v>
       </c>
       <c r="B121" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C121" s="2">
         <v>45739.32653292824</v>
@@ -13722,13 +13734,13 @@
         <v>2966</v>
       </c>
       <c r="H121" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I121" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J121" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K121">
         <v>264</v>
@@ -13767,7 +13779,7 @@
         <v>19.46666667</v>
       </c>
       <c r="W121" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X121">
         <v>0.038889</v>
@@ -13799,7 +13811,7 @@
         <v>25</v>
       </c>
       <c r="B122" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C122" s="2">
         <v>45739.326908125</v>
@@ -13817,13 +13829,13 @@
         <v>2996</v>
       </c>
       <c r="H122" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I122" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J122" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K122">
         <v>275</v>
@@ -13862,7 +13874,7 @@
         <v>20.13333333</v>
       </c>
       <c r="W122" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X122">
         <v>0.022222</v>
@@ -13894,7 +13906,7 @@
         <v>25</v>
       </c>
       <c r="B123" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C123" s="2">
         <v>45739.32722672453</v>
@@ -13912,13 +13924,13 @@
         <v>3026</v>
       </c>
       <c r="H123" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I123" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J123" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K123">
         <v>262</v>
@@ -13957,7 +13969,7 @@
         <v>19.9</v>
       </c>
       <c r="W123" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X123">
         <v>-0.007778</v>
@@ -13989,7 +14001,7 @@
         <v>25</v>
       </c>
       <c r="B124" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C124" s="2">
         <v>45739.32760277778</v>
@@ -14007,13 +14019,13 @@
         <v>3056</v>
       </c>
       <c r="H124" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I124" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="J124" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K124">
         <v>238</v>
@@ -14052,7 +14064,7 @@
         <v>19.86666667</v>
       </c>
       <c r="W124" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X124">
         <v>-0.001111</v>
@@ -14084,7 +14096,7 @@
         <v>25</v>
       </c>
       <c r="B125" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C125" s="2">
         <v>45739.32792096065</v>
@@ -14102,13 +14114,13 @@
         <v>3086</v>
       </c>
       <c r="H125" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I125" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J125" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K125">
         <v>239</v>
@@ -14147,7 +14159,7 @@
         <v>19.2</v>
       </c>
       <c r="W125" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X125">
         <v>-0.022222</v>
@@ -14179,7 +14191,7 @@
         <v>25</v>
       </c>
       <c r="B126" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C126" s="2">
         <v>45739.32829744213</v>
@@ -14197,13 +14209,13 @@
         <v>3116</v>
       </c>
       <c r="H126" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I126" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J126" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K126">
         <v>238</v>
@@ -14242,7 +14254,7 @@
         <v>19.06666667</v>
       </c>
       <c r="W126" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X126">
         <v>-0.004444</v>
@@ -14274,7 +14286,7 @@
         <v>25</v>
       </c>
       <c r="B127" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C127" s="2">
         <v>45739.32861597222</v>
@@ -14292,13 +14304,13 @@
         <v>3146</v>
       </c>
       <c r="H127" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I127" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J127" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K127">
         <v>244</v>
@@ -14337,7 +14349,7 @@
         <v>18.96666667</v>
       </c>
       <c r="W127" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X127">
         <v>-0.003333</v>
@@ -14369,7 +14381,7 @@
         <v>25</v>
       </c>
       <c r="B128" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C128" s="2">
         <v>45739.32899273148</v>
@@ -14387,13 +14399,13 @@
         <v>3176</v>
       </c>
       <c r="H128" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I128" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J128" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K128">
         <v>246</v>
@@ -14432,7 +14444,7 @@
         <v>18</v>
       </c>
       <c r="W128" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X128">
         <v>-0.032222</v>
@@ -14464,7 +14476,7 @@
         <v>25</v>
       </c>
       <c r="B129" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C129" s="2">
         <v>45739.32931001158</v>
@@ -14482,13 +14494,13 @@
         <v>3206</v>
       </c>
       <c r="H129" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I129" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J129" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K129">
         <v>233</v>
@@ -14527,7 +14539,7 @@
         <v>17.76666667</v>
       </c>
       <c r="W129" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X129">
         <v>-0.007778</v>
@@ -14559,7 +14571,7 @@
         <v>25</v>
       </c>
       <c r="B130" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C130" s="2">
         <v>45739.3296865625</v>
@@ -14577,13 +14589,13 @@
         <v>3236</v>
       </c>
       <c r="H130" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I130" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J130" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="K130">
         <v>236</v>
@@ -14622,7 +14634,7 @@
         <v>18.06666667</v>
       </c>
       <c r="W130" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X130">
         <v>0.01</v>
@@ -14654,7 +14666,7 @@
         <v>25</v>
       </c>
       <c r="B131" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C131" s="2">
         <v>45739.33000548611</v>
@@ -14672,13 +14684,13 @@
         <v>3266</v>
       </c>
       <c r="H131" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I131" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J131" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K131">
         <v>240</v>
@@ -14717,7 +14729,7 @@
         <v>17.6</v>
       </c>
       <c r="W131" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X131">
         <v>-0.015556</v>
@@ -14749,7 +14761,7 @@
         <v>25</v>
       </c>
       <c r="B132" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C132" s="2">
         <v>45739.33038180556</v>
@@ -14767,13 +14779,13 @@
         <v>3296</v>
       </c>
       <c r="H132" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I132" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J132" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="K132">
         <v>252</v>
@@ -14812,7 +14824,7 @@
         <v>18.43333333</v>
       </c>
       <c r="W132" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X132">
         <v>0.027778</v>
@@ -14844,7 +14856,7 @@
         <v>25</v>
       </c>
       <c r="B133" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C133" s="2">
         <v>45739.33069925926</v>
@@ -14862,13 +14874,13 @@
         <v>3326</v>
       </c>
       <c r="H133" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I133" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J133" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K133">
         <v>258</v>
@@ -14907,7 +14919,7 @@
         <v>18.06666667</v>
       </c>
       <c r="W133" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X133">
         <v>-0.012222</v>
@@ -14939,7 +14951,7 @@
         <v>25</v>
       </c>
       <c r="B134" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C134" s="2">
         <v>45739.33107539352</v>
@@ -14957,13 +14969,13 @@
         <v>3356</v>
       </c>
       <c r="H134" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I134" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J134" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K134">
         <v>251</v>
@@ -15002,7 +15014,7 @@
         <v>18.13333333</v>
       </c>
       <c r="W134" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X134">
         <v>0.002222</v>
@@ -15034,7 +15046,7 @@
         <v>25</v>
       </c>
       <c r="B135" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C135" s="2">
         <v>45739.33177121528</v>
@@ -15052,13 +15064,13 @@
         <v>3416</v>
       </c>
       <c r="H135" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I135" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J135" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K135">
         <v>245</v>
@@ -15097,7 +15109,7 @@
         <v>19.3</v>
       </c>
       <c r="W135" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X135">
         <v>0.019444</v>
@@ -15129,7 +15141,7 @@
         <v>25</v>
       </c>
       <c r="B136" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C136" s="2">
         <v>45739.3320884838</v>
@@ -15147,13 +15159,13 @@
         <v>3446</v>
       </c>
       <c r="H136" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I136" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J136" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K136">
         <v>239</v>
@@ -15192,7 +15204,7 @@
         <v>20.6</v>
       </c>
       <c r="W136" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X136">
         <v>0.043333</v>
@@ -15224,7 +15236,7 @@
         <v>25</v>
       </c>
       <c r="B137" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C137" s="2">
         <v>45739.33246533565</v>
@@ -15242,13 +15254,13 @@
         <v>3476</v>
       </c>
       <c r="H137" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I137" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J137" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K137">
         <v>236</v>
@@ -15287,7 +15299,7 @@
         <v>19.7</v>
       </c>
       <c r="W137" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X137">
         <v>-0.03</v>
@@ -15319,7 +15331,7 @@
         <v>25</v>
       </c>
       <c r="B138" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C138" s="2">
         <v>45739.33278344908</v>
@@ -15337,13 +15349,13 @@
         <v>3506</v>
       </c>
       <c r="H138" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I138" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="J138" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K138">
         <v>241</v>
@@ -15382,7 +15394,7 @@
         <v>19.56666667</v>
       </c>
       <c r="W138" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X138">
         <v>-0.004444</v>
@@ -15414,7 +15426,7 @@
         <v>25</v>
       </c>
       <c r="B139" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C139" s="2">
         <v>45739.33316055556</v>
@@ -15432,13 +15444,13 @@
         <v>3536</v>
       </c>
       <c r="H139" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I139" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J139" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K139">
         <v>244</v>
@@ -15477,7 +15489,7 @@
         <v>18.76666667</v>
       </c>
       <c r="W139" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X139">
         <v>-0.026667</v>
@@ -15509,7 +15521,7 @@
         <v>25</v>
       </c>
       <c r="B140" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C140" s="2">
         <v>45739.33347810185</v>
@@ -15527,13 +15539,13 @@
         <v>3566</v>
       </c>
       <c r="H140" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I140" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J140" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="K140">
         <v>249</v>
@@ -15572,7 +15584,7 @@
         <v>17.66666667</v>
       </c>
       <c r="W140" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X140">
         <v>-0.036667</v>
@@ -15604,7 +15616,7 @@
         <v>25</v>
       </c>
       <c r="B141" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C141" s="2">
         <v>45739.33385436342</v>
@@ -15622,13 +15634,13 @@
         <v>3596</v>
       </c>
       <c r="H141" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I141" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J141" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="K141">
         <v>256</v>
@@ -15667,7 +15679,7 @@
         <v>19.4</v>
       </c>
       <c r="W141" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X141">
         <v>0.057778</v>
@@ -15699,7 +15711,7 @@
         <v>25</v>
       </c>
       <c r="B142" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C142" s="2">
         <v>45739.33417287037</v>
@@ -15717,13 +15729,13 @@
         <v>3626</v>
       </c>
       <c r="H142" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I142" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J142" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K142">
         <v>245</v>
@@ -15762,7 +15774,7 @@
         <v>19.06666667</v>
       </c>
       <c r="W142" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X142">
         <v>-0.011111</v>
@@ -15794,7 +15806,7 @@
         <v>25</v>
       </c>
       <c r="B143" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C143" s="2">
         <v>45739.33454875</v>
@@ -15812,13 +15824,13 @@
         <v>3656</v>
       </c>
       <c r="H143" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I143" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="J143" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K143">
         <v>249</v>
@@ -15857,7 +15869,7 @@
         <v>19.13333333</v>
       </c>
       <c r="W143" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X143">
         <v>0.002222</v>
@@ -15889,7 +15901,7 @@
         <v>25</v>
       </c>
       <c r="B144" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C144" s="2">
         <v>45739.33456696759</v>
@@ -15907,13 +15919,13 @@
         <v>3660</v>
       </c>
       <c r="H144" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I144" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J144" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K144">
         <v>249</v>
@@ -15952,7 +15964,7 @@
         <v>22.83645833</v>
       </c>
       <c r="W144" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X144">
         <v>0.001286</v>
@@ -15984,7 +15996,7 @@
         <v>25</v>
       </c>
       <c r="B145" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C145" s="2">
         <v>45739.33486728009</v>
@@ -16002,13 +16014,13 @@
         <v>3686</v>
       </c>
       <c r="H145" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I145" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J145" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="K145">
         <v>255</v>
@@ -16047,7 +16059,7 @@
         <v>20.06666667</v>
       </c>
       <c r="W145" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X145">
         <v>-0.09232600000000001</v>
@@ -16079,7 +16091,7 @@
         <v>25</v>
       </c>
       <c r="B146" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C146" s="2">
         <v>45739.33494449074</v>
@@ -16097,13 +16109,13 @@
         <v>3690</v>
       </c>
       <c r="H146" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I146" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J146" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K146">
         <v>261</v>
@@ -16142,7 +16154,7 @@
         <v>20.46666667</v>
       </c>
       <c r="W146" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X146">
         <v>0.013333</v>
@@ -16174,7 +16186,7 @@
         <v>25</v>
       </c>
       <c r="B147" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C147" s="2">
         <v>45739.33524380787</v>
@@ -16192,13 +16204,13 @@
         <v>3716</v>
       </c>
       <c r="H147" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I147" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J147" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K147">
         <v>266</v>
@@ -16237,7 +16249,7 @@
         <v>19.26666667</v>
       </c>
       <c r="W147" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X147">
         <v>-0.04</v>
@@ -16269,7 +16281,7 @@
         <v>25</v>
       </c>
       <c r="B148" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C148" s="2">
         <v>45739.33526194444</v>
@@ -16287,13 +16299,13 @@
         <v>3720</v>
       </c>
       <c r="H148" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I148" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J148" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="K148">
         <v>267</v>
@@ -16332,7 +16344,7 @@
         <v>18.73333333</v>
       </c>
       <c r="W148" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X148">
         <v>-0.017778</v>
@@ -16364,7 +16376,7 @@
         <v>25</v>
       </c>
       <c r="B149" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C149" s="2">
         <v>45739.3355622338</v>
@@ -16382,13 +16394,13 @@
         <v>3746</v>
       </c>
       <c r="H149" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I149" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="J149" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K149">
         <v>262</v>
@@ -16427,7 +16439,7 @@
         <v>17.93333333</v>
       </c>
       <c r="W149" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X149">
         <v>-0.026667</v>
@@ -16459,7 +16471,7 @@
         <v>25</v>
       </c>
       <c r="B150" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C150" s="2">
         <v>45739.33563167824</v>
@@ -16477,13 +16489,13 @@
         <v>3750</v>
       </c>
       <c r="H150" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I150" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="J150" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K150">
         <v>263</v>
@@ -16522,7 +16534,7 @@
         <v>18.26666667</v>
       </c>
       <c r="W150" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X150">
         <v>0.011111</v>
@@ -16554,7 +16566,7 @@
         <v>25</v>
       </c>
       <c r="B151" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C151" s="2">
         <v>45739.33593381944</v>
@@ -16572,13 +16584,13 @@
         <v>3776</v>
       </c>
       <c r="H151" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I151" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="J151" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="K151">
         <v>260</v>
@@ -16617,7 +16629,7 @@
         <v>18.33333333</v>
       </c>
       <c r="W151" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X151">
         <v>0.002222</v>
@@ -16649,7 +16661,7 @@
         <v>25</v>
       </c>
       <c r="B152" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C152" s="2">
         <v>45739.3359505787</v>
@@ -16667,13 +16679,13 @@
         <v>3780</v>
       </c>
       <c r="H152" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I152" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J152" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K152">
         <v>259</v>
@@ -16712,7 +16724,7 @@
         <v>18.06666667</v>
       </c>
       <c r="W152" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X152">
         <v>-0.008888999999999999</v>
@@ -16744,7 +16756,7 @@
         <v>25</v>
       </c>
       <c r="B153" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C153" s="2">
         <v>45739.33625267361</v>
@@ -16762,13 +16774,13 @@
         <v>3806</v>
       </c>
       <c r="H153" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I153" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J153" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K153">
         <v>260</v>
@@ -16807,7 +16819,7 @@
         <v>17.76666667</v>
       </c>
       <c r="W153" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X153">
         <v>-0.01</v>
@@ -16839,7 +16851,7 @@
         <v>25</v>
       </c>
       <c r="B154" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C154" s="2">
         <v>45739.33632728009</v>
@@ -16857,13 +16869,13 @@
         <v>3810</v>
       </c>
       <c r="H154" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I154" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="J154" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="K154">
         <v>263</v>
@@ -16902,7 +16914,7 @@
         <v>17.63333333</v>
       </c>
       <c r="W154" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X154">
         <v>-0.004444</v>
@@ -16934,7 +16946,7 @@
         <v>25</v>
       </c>
       <c r="B155" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C155" s="2">
         <v>45739.33662940972</v>
@@ -16952,13 +16964,13 @@
         <v>3836</v>
       </c>
       <c r="H155" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I155" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J155" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="K155">
         <v>263</v>
@@ -16997,7 +17009,7 @@
         <v>17.83333333</v>
       </c>
       <c r="W155" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X155">
         <v>0.006667</v>
@@ -17029,7 +17041,7 @@
         <v>25</v>
       </c>
       <c r="B156" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C156" s="2">
         <v>45739.33664547453</v>
@@ -17047,13 +17059,13 @@
         <v>3840</v>
       </c>
       <c r="H156" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I156" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="J156" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K156">
         <v>268</v>
@@ -17092,7 +17104,7 @@
         <v>17.8</v>
       </c>
       <c r="W156" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X156">
         <v>-0.001111</v>
@@ -17124,7 +17136,7 @@
         <v>25</v>
       </c>
       <c r="B157" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C157" s="2">
         <v>45739.33694778935</v>
@@ -17142,13 +17154,13 @@
         <v>3866</v>
       </c>
       <c r="H157" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I157" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J157" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K157">
         <v>267</v>
@@ -17187,7 +17199,7 @@
         <v>18.43333333</v>
       </c>
       <c r="W157" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X157">
         <v>0.021111</v>
@@ -17219,7 +17231,7 @@
         <v>25</v>
       </c>
       <c r="B158" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C158" s="2">
         <v>45739.33732395833</v>
@@ -17237,13 +17249,13 @@
         <v>3896</v>
       </c>
       <c r="H158" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I158" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="J158" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K158">
         <v>263</v>
@@ -17282,7 +17294,7 @@
         <v>18.36666667</v>
       </c>
       <c r="W158" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X158">
         <v>-0.002222</v>
@@ -17314,7 +17326,7 @@
         <v>25</v>
       </c>
       <c r="B159" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C159" s="2">
         <v>45739.33734025463</v>
@@ -17332,13 +17344,13 @@
         <v>3900</v>
       </c>
       <c r="H159" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I159" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J159" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="K159">
         <v>258</v>
@@ -17377,7 +17389,7 @@
         <v>18.48333333</v>
       </c>
       <c r="W159" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X159">
         <v>0.001944</v>
@@ -17409,7 +17421,7 @@
         <v>25</v>
       </c>
       <c r="B160" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C160" s="2">
         <v>45739.33775258102</v>
@@ -17427,13 +17439,13 @@
         <v>3926</v>
       </c>
       <c r="H160" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I160" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J160" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K160">
         <v>260</v>
@@ -17472,7 +17484,7 @@
         <v>17.96666667</v>
       </c>
       <c r="W160" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X160">
         <v>-0.017222</v>
@@ -17506,10 +17518,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE100"/>
+  <dimension ref="A1:AF100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:32">
       <c r="A1" s="1" t="s">
         <v>39</v>
       </c>
@@ -17603,13 +17615,16 @@
       <c r="AE1" s="1" t="s">
         <v>69</v>
       </c>
+      <c r="AF1" s="1" t="s">
+        <v>70</v>
+      </c>
     </row>
-    <row r="2" spans="1:31">
+    <row r="2" spans="1:32">
       <c r="A2" t="s">
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C2" s="2">
         <v>45739.33801842593</v>
@@ -17627,13 +17642,13 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="J2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="K2">
         <v>267</v>
@@ -17672,7 +17687,7 @@
         <v>-140.2</v>
       </c>
       <c r="W2" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="Y2">
         <v>-140.2</v>
@@ -17681,12 +17696,12 @@
         <v>-140.275429</v>
       </c>
     </row>
-    <row r="3" spans="1:31">
+    <row r="3" spans="1:32">
       <c r="A3" t="s">
         <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C3" s="2">
         <v>45739.33833671296</v>
@@ -17704,13 +17719,13 @@
         <v>30</v>
       </c>
       <c r="H3" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I3" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="J3" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="K3">
         <v>240</v>
@@ -17749,7 +17764,7 @@
         <v>-144.1</v>
       </c>
       <c r="W3" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X3">
         <v>-0.13</v>
@@ -17770,12 +17785,12 @@
         <v>-143.434243</v>
       </c>
     </row>
-    <row r="4" spans="1:31">
+    <row r="4" spans="1:32">
       <c r="A4" t="s">
         <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C4" s="2">
         <v>45739.33871381944</v>
@@ -17793,13 +17808,13 @@
         <v>60</v>
       </c>
       <c r="H4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="J4" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="K4">
         <v>238</v>
@@ -17838,7 +17853,7 @@
         <v>-125.76666667</v>
       </c>
       <c r="W4" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X4">
         <v>0.611111</v>
@@ -17865,12 +17880,12 @@
         <v>-127.499189</v>
       </c>
     </row>
-    <row r="5" spans="1:31">
+    <row r="5" spans="1:32">
       <c r="A5" t="s">
         <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C5" s="2">
         <v>45739.33903276621</v>
@@ -17888,13 +17903,13 @@
         <v>90</v>
       </c>
       <c r="H5" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I5" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="J5" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="K5">
         <v>259</v>
@@ -17933,7 +17948,7 @@
         <v>-112.5</v>
       </c>
       <c r="W5" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X5">
         <v>0.442222</v>
@@ -17960,12 +17975,12 @@
         <v>-111.644294</v>
       </c>
     </row>
-    <row r="6" spans="1:31">
+    <row r="6" spans="1:32">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C6" s="2">
         <v>45739.33940880787</v>
@@ -17983,13 +17998,13 @@
         <v>120</v>
       </c>
       <c r="H6" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I6" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="J6" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="K6">
         <v>300</v>
@@ -18028,7 +18043,7 @@
         <v>-101.26666667</v>
       </c>
       <c r="W6" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X6">
         <v>0.374444</v>
@@ -18055,12 +18070,12 @@
         <v>-100.10081</v>
       </c>
     </row>
-    <row r="7" spans="1:31">
+    <row r="7" spans="1:32">
       <c r="A7" t="s">
         <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C7" s="2">
         <v>45739.33972710648</v>
@@ -18078,13 +18093,13 @@
         <v>150</v>
       </c>
       <c r="H7" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I7" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="J7" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="K7">
         <v>260</v>
@@ -18123,7 +18138,7 @@
         <v>-93.83333333</v>
       </c>
       <c r="W7" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X7">
         <v>0.247778</v>
@@ -18150,12 +18165,12 @@
         <v>-92.49723299999999</v>
       </c>
     </row>
-    <row r="8" spans="1:31">
+    <row r="8" spans="1:32">
       <c r="A8" t="s">
         <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C8" s="2">
         <v>45739.3401037037</v>
@@ -18173,13 +18188,13 @@
         <v>180</v>
       </c>
       <c r="H8" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I8" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="J8" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="K8">
         <v>181</v>
@@ -18218,7 +18233,7 @@
         <v>-85.83333333</v>
       </c>
       <c r="W8" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X8">
         <v>0.266667</v>
@@ -18245,12 +18260,12 @@
         <v>-87.460204</v>
       </c>
     </row>
-    <row r="9" spans="1:31">
+    <row r="9" spans="1:32">
       <c r="A9" t="s">
         <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C9" s="2">
         <v>45739.34042210648</v>
@@ -18268,13 +18283,13 @@
         <v>210</v>
       </c>
       <c r="H9" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I9" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="J9" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="K9">
         <v>211</v>
@@ -18313,7 +18328,7 @@
         <v>-80.56666667</v>
       </c>
       <c r="W9" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X9">
         <v>0.175556</v>
@@ -18340,12 +18355,12 @@
         <v>-83.347216</v>
       </c>
     </row>
-    <row r="10" spans="1:31">
+    <row r="10" spans="1:32">
       <c r="A10" t="s">
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C10" s="2">
         <v>45739.34079809028</v>
@@ -18363,13 +18378,13 @@
         <v>240</v>
       </c>
       <c r="H10" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I10" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="J10" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="K10">
         <v>150</v>
@@ -18408,7 +18423,7 @@
         <v>-78.09999999999999</v>
       </c>
       <c r="W10" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X10">
         <v>0.082222</v>
@@ -18435,12 +18450,12 @@
         <v>-79.028886</v>
       </c>
     </row>
-    <row r="11" spans="1:31">
+    <row r="11" spans="1:32">
       <c r="A11" t="s">
         <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C11" s="2">
         <v>45739.34111708334</v>
@@ -18458,13 +18473,13 @@
         <v>270</v>
       </c>
       <c r="H11" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I11" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="J11" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="K11">
         <v>47</v>
@@ -18503,7 +18518,7 @@
         <v>-74.06666667</v>
       </c>
       <c r="W11" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X11">
         <v>0.134444</v>
@@ -18530,12 +18545,12 @@
         <v>-74.124393</v>
       </c>
     </row>
-    <row r="12" spans="1:31">
+    <row r="12" spans="1:32">
       <c r="A12" t="s">
         <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C12" s="2">
         <v>45739.34149304398</v>
@@ -18553,13 +18568,13 @@
         <v>300</v>
       </c>
       <c r="H12" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I12" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="J12" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="K12">
         <v>116</v>
@@ -18598,7 +18613,7 @@
         <v>-70.90000000000001</v>
       </c>
       <c r="W12" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X12">
         <v>0.105556</v>
@@ -18625,12 +18640,12 @@
         <v>-68.576373</v>
       </c>
     </row>
-    <row r="13" spans="1:31">
+    <row r="13" spans="1:32">
       <c r="A13" t="s">
         <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C13" s="2">
         <v>45739.34181186343</v>
@@ -18648,13 +18663,13 @@
         <v>330</v>
       </c>
       <c r="H13" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I13" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="J13" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="K13">
         <v>169</v>
@@ -18693,7 +18708,7 @@
         <v>-68.09999999999999</v>
       </c>
       <c r="W13" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X13">
         <v>0.093333</v>
@@ -18720,12 +18735,12 @@
         <v>-62.633238</v>
       </c>
     </row>
-    <row r="14" spans="1:31">
+    <row r="14" spans="1:32">
       <c r="A14" t="s">
         <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C14" s="2">
         <v>45739.34218833334</v>
@@ -18743,13 +18758,13 @@
         <v>360</v>
       </c>
       <c r="H14" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I14" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="J14" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="K14">
         <v>142</v>
@@ -18788,7 +18803,7 @@
         <v>-64.63333333</v>
       </c>
       <c r="W14" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X14">
         <v>0.115556</v>
@@ -18815,12 +18830,12 @@
         <v>-56.751968</v>
       </c>
     </row>
-    <row r="15" spans="1:31">
+    <row r="15" spans="1:32">
       <c r="A15" t="s">
         <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C15" s="2">
         <v>45739.34250637732</v>
@@ -18838,13 +18853,13 @@
         <v>390</v>
       </c>
       <c r="H15" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I15" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="J15" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="K15">
         <v>119</v>
@@ -18883,7 +18898,7 @@
         <v>-45.96666667</v>
       </c>
       <c r="W15" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X15">
         <v>0.6222220000000001</v>
@@ -18910,12 +18925,12 @@
         <v>-52.631044</v>
       </c>
     </row>
-    <row r="16" spans="1:31">
+    <row r="16" spans="1:32">
       <c r="A16" t="s">
         <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C16" s="2">
         <v>45739.34288298611</v>
@@ -18933,13 +18948,13 @@
         <v>420</v>
       </c>
       <c r="H16" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I16" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="J16" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="K16">
         <v>123</v>
@@ -18978,7 +18993,7 @@
         <v>-43.36666667</v>
       </c>
       <c r="W16" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X16">
         <v>0.08666699999999999</v>
@@ -19010,7 +19025,7 @@
         <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C17" s="2">
         <v>45739.34319527778</v>
@@ -19028,13 +19043,13 @@
         <v>450</v>
       </c>
       <c r="H17" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I17" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="J17" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="K17">
         <v>58</v>
@@ -19073,7 +19088,7 @@
         <v>-41.3</v>
       </c>
       <c r="W17" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X17">
         <v>0.06888900000000001</v>
@@ -19105,7 +19120,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C18" s="2">
         <v>45739.34357434028</v>
@@ -19123,13 +19138,13 @@
         <v>480</v>
       </c>
       <c r="H18" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I18" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="J18" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="K18">
         <v>37</v>
@@ -19168,7 +19183,7 @@
         <v>-40.9</v>
       </c>
       <c r="W18" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X18">
         <v>0.013333</v>
@@ -19200,7 +19215,7 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C19" s="2">
         <v>45739.34389346065</v>
@@ -19218,13 +19233,13 @@
         <v>510</v>
       </c>
       <c r="H19" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I19" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="J19" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="K19">
         <v>61</v>
@@ -19263,7 +19278,7 @@
         <v>-39.46666667</v>
       </c>
       <c r="W19" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X19">
         <v>0.047778</v>
@@ -19295,7 +19310,7 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C20" s="2">
         <v>45739.34427020833</v>
@@ -19313,13 +19328,13 @@
         <v>540</v>
       </c>
       <c r="H20" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I20" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="J20" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="K20">
         <v>95</v>
@@ -19358,7 +19373,7 @@
         <v>-38.36666667</v>
       </c>
       <c r="W20" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X20">
         <v>0.036667</v>
@@ -19390,7 +19405,7 @@
         <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C21" s="2">
         <v>45739.34458828704</v>
@@ -19408,13 +19423,13 @@
         <v>570</v>
       </c>
       <c r="H21" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I21" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="J21" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="K21">
         <v>94</v>
@@ -19453,7 +19468,7 @@
         <v>-38.9</v>
       </c>
       <c r="W21" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X21">
         <v>-0.017778</v>
@@ -19485,7 +19500,7 @@
         <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C22" s="2">
         <v>45739.34496434028</v>
@@ -19503,13 +19518,13 @@
         <v>600</v>
       </c>
       <c r="H22" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I22" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="J22" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="K22">
         <v>120</v>
@@ -19548,7 +19563,7 @@
         <v>-36.86666667</v>
       </c>
       <c r="W22" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X22">
         <v>0.067778</v>
@@ -19580,7 +19595,7 @@
         <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C23" s="2">
         <v>45739.3452833912</v>
@@ -19598,13 +19613,13 @@
         <v>630</v>
       </c>
       <c r="H23" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I23" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="J23" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="K23">
         <v>152</v>
@@ -19643,7 +19658,7 @@
         <v>-36.56666667</v>
       </c>
       <c r="W23" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X23">
         <v>0.01</v>
@@ -19675,7 +19690,7 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C24" s="2">
         <v>45739.34565917824</v>
@@ -19693,13 +19708,13 @@
         <v>660</v>
       </c>
       <c r="H24" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I24" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="J24" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K24">
         <v>122</v>
@@ -19738,7 +19753,7 @@
         <v>-34.3</v>
       </c>
       <c r="W24" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X24">
         <v>0.075556</v>
@@ -19770,7 +19785,7 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C25" s="2">
         <v>45739.34597869213</v>
@@ -19788,13 +19803,13 @@
         <v>690</v>
       </c>
       <c r="H25" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I25" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="J25" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="K25">
         <v>114</v>
@@ -19833,7 +19848,7 @@
         <v>-32.83333333</v>
       </c>
       <c r="W25" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X25">
         <v>0.048889</v>
@@ -19865,7 +19880,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C26" s="2">
         <v>45739.34635144676</v>
@@ -19883,13 +19898,13 @@
         <v>720</v>
       </c>
       <c r="H26" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I26" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="J26" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="K26">
         <v>128</v>
@@ -19928,7 +19943,7 @@
         <v>-31.86666667</v>
       </c>
       <c r="W26" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X26">
         <v>0.032222</v>
@@ -19960,7 +19975,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C27" s="2">
         <v>45739.34667371528</v>
@@ -19978,13 +19993,13 @@
         <v>750</v>
       </c>
       <c r="H27" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I27" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="J27" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="K27">
         <v>118</v>
@@ -20023,7 +20038,7 @@
         <v>-31.43333333</v>
       </c>
       <c r="W27" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X27">
         <v>0.014444</v>
@@ -20055,7 +20070,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C28" s="2">
         <v>45739.34704778935</v>
@@ -20073,13 +20088,13 @@
         <v>780</v>
       </c>
       <c r="H28" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I28" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="J28" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="K28">
         <v>113</v>
@@ -20118,7 +20133,7 @@
         <v>-32.06666667</v>
       </c>
       <c r="W28" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X28">
         <v>-0.021111</v>
@@ -20150,7 +20165,7 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C29" s="2">
         <v>45739.34736730324</v>
@@ -20168,13 +20183,13 @@
         <v>810</v>
       </c>
       <c r="H29" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I29" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="J29" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="K29">
         <v>104</v>
@@ -20213,7 +20228,7 @@
         <v>-32.33333333</v>
       </c>
       <c r="W29" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X29">
         <v>-0.008888999999999999</v>
@@ -20245,7 +20260,7 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C30" s="2">
         <v>45739.34774370371</v>
@@ -20263,13 +20278,13 @@
         <v>840</v>
       </c>
       <c r="H30" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I30" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="J30" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="K30">
         <v>95</v>
@@ -20308,7 +20323,7 @@
         <v>-31</v>
       </c>
       <c r="W30" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X30">
         <v>0.044444</v>
@@ -20340,7 +20355,7 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C31" s="2">
         <v>45739.34805827546</v>
@@ -20358,13 +20373,13 @@
         <v>870</v>
       </c>
       <c r="H31" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I31" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="J31" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="K31">
         <v>101</v>
@@ -20403,7 +20418,7 @@
         <v>-29.46666667</v>
       </c>
       <c r="W31" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X31">
         <v>0.051111</v>
@@ -20435,7 +20450,7 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C32" s="2">
         <v>45739.34843116898</v>
@@ -20453,13 +20468,13 @@
         <v>900</v>
       </c>
       <c r="H32" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I32" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="J32" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="K32">
         <v>117</v>
@@ -20498,7 +20513,7 @@
         <v>-28.86666667</v>
       </c>
       <c r="W32" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X32">
         <v>0.02</v>
@@ -20530,7 +20545,7 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C33" s="2">
         <v>45739.34875561343</v>
@@ -20548,13 +20563,13 @@
         <v>930</v>
       </c>
       <c r="H33" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I33" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="J33" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="K33">
         <v>97</v>
@@ -20593,7 +20608,7 @@
         <v>-26.5</v>
       </c>
       <c r="W33" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X33">
         <v>0.078889</v>
@@ -20625,7 +20640,7 @@
         <v>25</v>
       </c>
       <c r="B34" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C34" s="2">
         <v>45739.34913115741</v>
@@ -20643,13 +20658,13 @@
         <v>960</v>
       </c>
       <c r="H34" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I34" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="J34" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="K34">
         <v>92</v>
@@ -20688,7 +20703,7 @@
         <v>-27.3</v>
       </c>
       <c r="W34" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X34">
         <v>-0.026667</v>
@@ -20720,7 +20735,7 @@
         <v>25</v>
       </c>
       <c r="B35" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C35" s="2">
         <v>45739.34944959491</v>
@@ -20738,13 +20753,13 @@
         <v>990</v>
       </c>
       <c r="H35" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I35" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="J35" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="K35">
         <v>92</v>
@@ -20783,7 +20798,7 @@
         <v>-26.23333333</v>
       </c>
       <c r="W35" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X35">
         <v>0.035556</v>
@@ -20815,7 +20830,7 @@
         <v>25</v>
       </c>
       <c r="B36" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C36" s="2">
         <v>45739.34982219907</v>
@@ -20833,13 +20848,13 @@
         <v>1020</v>
       </c>
       <c r="H36" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I36" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="J36" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="K36">
         <v>96</v>
@@ -20878,7 +20893,7 @@
         <v>-26.73333333</v>
       </c>
       <c r="W36" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X36">
         <v>-0.016667</v>
@@ -20910,7 +20925,7 @@
         <v>25</v>
       </c>
       <c r="B37" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C37" s="2">
         <v>45739.35014129629</v>
@@ -20928,13 +20943,13 @@
         <v>1050</v>
       </c>
       <c r="H37" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I37" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="J37" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="K37">
         <v>96</v>
@@ -20973,7 +20988,7 @@
         <v>-27.5</v>
       </c>
       <c r="W37" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X37">
         <v>-0.025556</v>
@@ -21005,7 +21020,7 @@
         <v>25</v>
       </c>
       <c r="B38" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C38" s="2">
         <v>45739.35051763889</v>
@@ -21023,13 +21038,13 @@
         <v>1080</v>
       </c>
       <c r="H38" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I38" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="J38" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="K38">
         <v>99</v>
@@ -21068,7 +21083,7 @@
         <v>-27.2</v>
       </c>
       <c r="W38" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X38">
         <v>0.01</v>
@@ -21100,7 +21115,7 @@
         <v>25</v>
       </c>
       <c r="B39" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C39" s="2">
         <v>45739.35083655093</v>
@@ -21118,13 +21133,13 @@
         <v>1110</v>
       </c>
       <c r="H39" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I39" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="J39" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="K39">
         <v>98</v>
@@ -21163,7 +21178,7 @@
         <v>-25.4</v>
       </c>
       <c r="W39" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X39">
         <v>0.06</v>
@@ -21195,7 +21210,7 @@
         <v>25</v>
       </c>
       <c r="B40" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C40" s="2">
         <v>45739.35121329861</v>
@@ -21213,13 +21228,13 @@
         <v>1140</v>
       </c>
       <c r="H40" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I40" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="J40" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="K40">
         <v>93</v>
@@ -21258,7 +21273,7 @@
         <v>-26.26666667</v>
       </c>
       <c r="W40" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X40">
         <v>-0.028889</v>
@@ -21290,7 +21305,7 @@
         <v>25</v>
       </c>
       <c r="B41" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C41" s="2">
         <v>45739.35153231482</v>
@@ -21308,13 +21323,13 @@
         <v>1170</v>
       </c>
       <c r="H41" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I41" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="J41" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="K41">
         <v>98</v>
@@ -21353,7 +21368,7 @@
         <v>-24.8</v>
       </c>
       <c r="W41" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X41">
         <v>0.048889</v>
@@ -21385,7 +21400,7 @@
         <v>25</v>
       </c>
       <c r="B42" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C42" s="2">
         <v>45739.35190940972</v>
@@ -21403,13 +21418,13 @@
         <v>1200</v>
       </c>
       <c r="H42" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I42" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="J42" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="K42">
         <v>101</v>
@@ -21448,7 +21463,7 @@
         <v>-24.63333333</v>
       </c>
       <c r="W42" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X42">
         <v>0.005556</v>
@@ -21480,7 +21495,7 @@
         <v>25</v>
       </c>
       <c r="B43" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C43" s="2">
         <v>45739.35222880787</v>
@@ -21498,13 +21513,13 @@
         <v>1230</v>
       </c>
       <c r="H43" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I43" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="J43" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="K43">
         <v>95</v>
@@ -21543,7 +21558,7 @@
         <v>-24.4</v>
       </c>
       <c r="W43" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X43">
         <v>0.007778</v>
@@ -21575,7 +21590,7 @@
         <v>25</v>
       </c>
       <c r="B44" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C44" s="2">
         <v>45739.35260185185</v>
@@ -21593,13 +21608,13 @@
         <v>1260</v>
       </c>
       <c r="H44" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I44" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="J44" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="K44">
         <v>98</v>
@@ -21638,7 +21653,7 @@
         <v>-24.23333333</v>
       </c>
       <c r="W44" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X44">
         <v>0.005556</v>
@@ -21670,7 +21685,7 @@
         <v>25</v>
       </c>
       <c r="B45" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C45" s="2">
         <v>45739.35292063657</v>
@@ -21688,13 +21703,13 @@
         <v>1290</v>
       </c>
       <c r="H45" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I45" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="J45" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="K45">
         <v>106</v>
@@ -21733,7 +21748,7 @@
         <v>-23.73333333</v>
       </c>
       <c r="W45" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X45">
         <v>0.016667</v>
@@ -21765,7 +21780,7 @@
         <v>25</v>
       </c>
       <c r="B46" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C46" s="2">
         <v>45739.35329739584</v>
@@ -21783,13 +21798,13 @@
         <v>1320</v>
       </c>
       <c r="H46" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I46" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="J46" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="K46">
         <v>100</v>
@@ -21828,7 +21843,7 @@
         <v>-23.23333333</v>
       </c>
       <c r="W46" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X46">
         <v>0.016667</v>
@@ -21860,7 +21875,7 @@
         <v>25</v>
       </c>
       <c r="B47" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C47" s="2">
         <v>45739.35361577546</v>
@@ -21878,13 +21893,13 @@
         <v>1350</v>
       </c>
       <c r="H47" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I47" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="J47" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="K47">
         <v>95</v>
@@ -21923,7 +21938,7 @@
         <v>-23.06666667</v>
       </c>
       <c r="W47" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X47">
         <v>0.005556</v>
@@ -21955,7 +21970,7 @@
         <v>25</v>
       </c>
       <c r="B48" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C48" s="2">
         <v>45739.35399203704</v>
@@ -21973,13 +21988,13 @@
         <v>1380</v>
       </c>
       <c r="H48" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I48" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="J48" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="K48">
         <v>111</v>
@@ -22018,7 +22033,7 @@
         <v>-22.46666667</v>
       </c>
       <c r="W48" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X48">
         <v>0.02</v>
@@ -22050,7 +22065,7 @@
         <v>25</v>
       </c>
       <c r="B49" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C49" s="2">
         <v>45739.35430842593</v>
@@ -22068,13 +22083,13 @@
         <v>1410</v>
       </c>
       <c r="H49" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I49" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="J49" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="K49">
         <v>111</v>
@@ -22113,7 +22128,7 @@
         <v>-22.6</v>
       </c>
       <c r="W49" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X49">
         <v>-0.004444</v>
@@ -22145,7 +22160,7 @@
         <v>25</v>
       </c>
       <c r="B50" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C50" s="2">
         <v>45739.35468496528</v>
@@ -22163,13 +22178,13 @@
         <v>1440</v>
       </c>
       <c r="H50" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I50" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="J50" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K50">
         <v>104</v>
@@ -22208,7 +22223,7 @@
         <v>-22.13333333</v>
       </c>
       <c r="W50" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X50">
         <v>0.015556</v>
@@ -22240,7 +22255,7 @@
         <v>25</v>
       </c>
       <c r="B51" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C51" s="2">
         <v>45739.35500327546</v>
@@ -22258,13 +22273,13 @@
         <v>1470</v>
       </c>
       <c r="H51" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I51" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="J51" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="K51">
         <v>106</v>
@@ -22303,7 +22318,7 @@
         <v>-21</v>
       </c>
       <c r="W51" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X51">
         <v>0.037778</v>
@@ -22335,7 +22350,7 @@
         <v>25</v>
       </c>
       <c r="B52" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C52" s="2">
         <v>45739.35538273148</v>
@@ -22353,13 +22368,13 @@
         <v>1500</v>
       </c>
       <c r="H52" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I52" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="J52" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="K52">
         <v>110</v>
@@ -22398,7 +22413,7 @@
         <v>-22.63333333</v>
       </c>
       <c r="W52" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X52">
         <v>-0.054444</v>
@@ -22430,7 +22445,7 @@
         <v>25</v>
       </c>
       <c r="B53" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C53" s="2">
         <v>45739.35569839121</v>
@@ -22448,13 +22463,13 @@
         <v>1530</v>
       </c>
       <c r="H53" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I53" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="J53" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="K53">
         <v>122</v>
@@ -22493,7 +22508,7 @@
         <v>-21.9</v>
       </c>
       <c r="W53" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X53">
         <v>0.024444</v>
@@ -22525,7 +22540,7 @@
         <v>25</v>
       </c>
       <c r="B54" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C54" s="2">
         <v>45739.3560770949</v>
@@ -22543,13 +22558,13 @@
         <v>1560</v>
       </c>
       <c r="H54" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I54" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="J54" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="K54">
         <v>115</v>
@@ -22588,7 +22603,7 @@
         <v>-20.9</v>
       </c>
       <c r="W54" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X54">
         <v>0.033333</v>
@@ -22620,7 +22635,7 @@
         <v>25</v>
       </c>
       <c r="B55" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C55" s="2">
         <v>45739.35639149306</v>
@@ -22638,13 +22653,13 @@
         <v>1590</v>
       </c>
       <c r="H55" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I55" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="J55" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="K55">
         <v>125</v>
@@ -22683,7 +22698,7 @@
         <v>-20.4</v>
       </c>
       <c r="W55" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X55">
         <v>0.016667</v>
@@ -22715,7 +22730,7 @@
         <v>25</v>
       </c>
       <c r="B56" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C56" s="2">
         <v>45739.356770625</v>
@@ -22733,13 +22748,13 @@
         <v>1620</v>
       </c>
       <c r="H56" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I56" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="J56" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="K56">
         <v>115</v>
@@ -22778,7 +22793,7 @@
         <v>-19.8</v>
       </c>
       <c r="W56" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X56">
         <v>0.02</v>
@@ -22810,7 +22825,7 @@
         <v>25</v>
       </c>
       <c r="B57" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C57" s="2">
         <v>45739.357089375</v>
@@ -22828,13 +22843,13 @@
         <v>1650</v>
       </c>
       <c r="H57" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I57" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J57" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="K57">
         <v>126</v>
@@ -22873,7 +22888,7 @@
         <v>-19.66666667</v>
       </c>
       <c r="W57" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X57">
         <v>0.004444</v>
@@ -22905,7 +22920,7 @@
         <v>25</v>
       </c>
       <c r="B58" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C58" s="2">
         <v>45739.35746126158</v>
@@ -22923,13 +22938,13 @@
         <v>1680</v>
       </c>
       <c r="H58" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I58" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="J58" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="K58">
         <v>117</v>
@@ -22968,7 +22983,7 @@
         <v>-19.16666667</v>
       </c>
       <c r="W58" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X58">
         <v>0.016667</v>
@@ -23000,7 +23015,7 @@
         <v>25</v>
       </c>
       <c r="B59" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C59" s="2">
         <v>45739.35778059028</v>
@@ -23018,13 +23033,13 @@
         <v>1710</v>
       </c>
       <c r="H59" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I59" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="J59" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="K59">
         <v>129</v>
@@ -23063,7 +23078,7 @@
         <v>-19.96666667</v>
       </c>
       <c r="W59" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X59">
         <v>-0.026667</v>
@@ -23095,7 +23110,7 @@
         <v>25</v>
       </c>
       <c r="B60" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C60" s="2">
         <v>45739.35847554398</v>
@@ -23113,13 +23128,13 @@
         <v>1770</v>
       </c>
       <c r="H60" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I60" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="J60" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="K60">
         <v>137</v>
@@ -23158,7 +23173,7 @@
         <v>-20</v>
       </c>
       <c r="W60" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X60">
         <v>-0.000556</v>
@@ -23190,7 +23205,7 @@
         <v>25</v>
       </c>
       <c r="B61" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C61" s="2">
         <v>45739.35885269676</v>
@@ -23208,13 +23223,13 @@
         <v>1800</v>
       </c>
       <c r="H61" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I61" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="J61" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="K61">
         <v>124</v>
@@ -23253,7 +23268,7 @@
         <v>-19</v>
       </c>
       <c r="W61" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X61">
         <v>0.033333</v>
@@ -23285,7 +23300,7 @@
         <v>25</v>
       </c>
       <c r="B62" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C62" s="2">
         <v>45739.35917258102</v>
@@ -23303,13 +23318,13 @@
         <v>1830</v>
       </c>
       <c r="H62" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I62" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="J62" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="K62">
         <v>131</v>
@@ -23348,7 +23363,7 @@
         <v>-18.36666667</v>
       </c>
       <c r="W62" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X62">
         <v>0.021111</v>
@@ -23380,7 +23395,7 @@
         <v>25</v>
       </c>
       <c r="B63" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C63" s="2">
         <v>45739.35954835648</v>
@@ -23398,13 +23413,13 @@
         <v>1860</v>
       </c>
       <c r="H63" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I63" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="J63" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="K63">
         <v>117</v>
@@ -23443,7 +23458,7 @@
         <v>-17.93333333</v>
       </c>
       <c r="W63" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X63">
         <v>0.014444</v>
@@ -23475,7 +23490,7 @@
         <v>25</v>
       </c>
       <c r="B64" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C64" s="2">
         <v>45739.35986782407</v>
@@ -23493,13 +23508,13 @@
         <v>1890</v>
       </c>
       <c r="H64" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I64" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="J64" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="K64">
         <v>117</v>
@@ -23538,7 +23553,7 @@
         <v>-18</v>
       </c>
       <c r="W64" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X64">
         <v>-0.002222</v>
@@ -23570,7 +23585,7 @@
         <v>25</v>
       </c>
       <c r="B65" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C65" s="2">
         <v>45739.36023918982</v>
@@ -23588,13 +23603,13 @@
         <v>1920</v>
       </c>
       <c r="H65" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I65" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="J65" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="K65">
         <v>121</v>
@@ -23633,7 +23648,7 @@
         <v>-18.5</v>
       </c>
       <c r="W65" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X65">
         <v>-0.016667</v>
@@ -23665,7 +23680,7 @@
         <v>25</v>
       </c>
       <c r="B66" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C66" s="2">
         <v>45739.36056288194</v>
@@ -23683,13 +23698,13 @@
         <v>1950</v>
       </c>
       <c r="H66" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I66" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="J66" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="K66">
         <v>124</v>
@@ -23728,7 +23743,7 @@
         <v>-17.66666667</v>
       </c>
       <c r="W66" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X66">
         <v>0.027778</v>
@@ -23760,7 +23775,7 @@
         <v>25</v>
       </c>
       <c r="B67" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C67" s="2">
         <v>45739.36093501157</v>
@@ -23778,13 +23793,13 @@
         <v>1980</v>
       </c>
       <c r="H67" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I67" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="J67" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="K67">
         <v>114</v>
@@ -23823,7 +23838,7 @@
         <v>-17.76666667</v>
       </c>
       <c r="W67" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X67">
         <v>-0.003333</v>
@@ -23855,7 +23870,7 @@
         <v>25</v>
       </c>
       <c r="B68" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C68" s="2">
         <v>45739.3612561574</v>
@@ -23873,13 +23888,13 @@
         <v>2010</v>
       </c>
       <c r="H68" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I68" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="J68" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="K68">
         <v>126</v>
@@ -23918,7 +23933,7 @@
         <v>-16.86666667</v>
       </c>
       <c r="W68" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X68">
         <v>0.03</v>
@@ -23950,7 +23965,7 @@
         <v>25</v>
       </c>
       <c r="B69" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C69" s="2">
         <v>45739.36163271991</v>
@@ -23968,13 +23983,13 @@
         <v>2040</v>
       </c>
       <c r="H69" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I69" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="J69" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="K69">
         <v>127</v>
@@ -24013,7 +24028,7 @@
         <v>-16.9</v>
       </c>
       <c r="W69" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X69">
         <v>-0.001111</v>
@@ -24045,7 +24060,7 @@
         <v>25</v>
       </c>
       <c r="B70" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C70" s="2">
         <v>45739.36194528935</v>
@@ -24063,13 +24078,13 @@
         <v>2070</v>
       </c>
       <c r="H70" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I70" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="J70" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="K70">
         <v>129</v>
@@ -24108,7 +24123,7 @@
         <v>-17.5</v>
       </c>
       <c r="W70" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X70">
         <v>-0.02</v>
@@ -24140,7 +24155,7 @@
         <v>25</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C71" s="2">
         <v>45739.36232252315</v>
@@ -24158,13 +24173,13 @@
         <v>2100</v>
       </c>
       <c r="H71" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I71" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="J71" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="K71">
         <v>129</v>
@@ -24203,7 +24218,7 @@
         <v>-17.76666667</v>
       </c>
       <c r="W71" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X71">
         <v>-0.008888999999999999</v>
@@ -24235,7 +24250,7 @@
         <v>25</v>
       </c>
       <c r="B72" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C72" s="2">
         <v>45739.36235965278</v>
@@ -24253,13 +24268,13 @@
         <v>2104</v>
       </c>
       <c r="H72" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I72" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="J72" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="K72">
         <v>125</v>
@@ -24298,7 +24313,7 @@
         <v>-38.09444444</v>
       </c>
       <c r="W72" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X72">
         <v>-0.009410999999999999</v>
@@ -24330,7 +24345,7 @@
         <v>25</v>
       </c>
       <c r="B73" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C73" s="2">
         <v>45739.36264126158</v>
@@ -24348,13 +24363,13 @@
         <v>2130</v>
       </c>
       <c r="H73" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I73" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="J73" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="K73">
         <v>121</v>
@@ -24393,7 +24408,7 @@
         <v>-18.2</v>
       </c>
       <c r="W73" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X73">
         <v>0.663148</v>
@@ -24425,7 +24440,7 @@
         <v>25</v>
       </c>
       <c r="B74" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C74" s="2">
         <v>45739.3627180787</v>
@@ -24443,13 +24458,13 @@
         <v>2134</v>
       </c>
       <c r="H74" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I74" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="J74" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="K74">
         <v>121</v>
@@ -24488,7 +24503,7 @@
         <v>-17.7</v>
       </c>
       <c r="W74" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X74">
         <v>0.016667</v>
@@ -24520,7 +24535,7 @@
         <v>25</v>
       </c>
       <c r="B75" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C75" s="2">
         <v>45739.36301694444</v>
@@ -24538,13 +24553,13 @@
         <v>2160</v>
       </c>
       <c r="H75" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I75" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="J75" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="K75">
         <v>133</v>
@@ -24583,7 +24598,7 @@
         <v>-18.36666667</v>
       </c>
       <c r="W75" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X75">
         <v>-0.022222</v>
@@ -24615,7 +24630,7 @@
         <v>25</v>
       </c>
       <c r="B76" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C76" s="2">
         <v>45739.36305766203</v>
@@ -24633,13 +24648,13 @@
         <v>2164</v>
       </c>
       <c r="H76" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I76" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="J76" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="K76">
         <v>135</v>
@@ -24678,7 +24693,7 @@
         <v>-18.9</v>
       </c>
       <c r="W76" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X76">
         <v>-0.017778</v>
@@ -24710,7 +24725,7 @@
         <v>25</v>
       </c>
       <c r="B77" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C77" s="2">
         <v>45739.36333483797</v>
@@ -24728,13 +24743,13 @@
         <v>2190</v>
       </c>
       <c r="H77" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I77" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="J77" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="K77">
         <v>115</v>
@@ -24773,7 +24788,7 @@
         <v>-17.8</v>
       </c>
       <c r="W77" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X77">
         <v>0.036667</v>
@@ -24805,7 +24820,7 @@
         <v>25</v>
       </c>
       <c r="B78" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C78" s="2">
         <v>45739.3634158912</v>
@@ -24823,13 +24838,13 @@
         <v>2194</v>
       </c>
       <c r="H78" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I78" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="J78" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="K78">
         <v>116</v>
@@ -24868,7 +24883,7 @@
         <v>-17.76666667</v>
       </c>
       <c r="W78" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X78">
         <v>0.001111</v>
@@ -24900,7 +24915,7 @@
         <v>25</v>
       </c>
       <c r="B79" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C79" s="2">
         <v>45739.36371184028</v>
@@ -24918,13 +24933,13 @@
         <v>2220</v>
       </c>
       <c r="H79" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I79" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="J79" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="K79">
         <v>118</v>
@@ -24963,7 +24978,7 @@
         <v>-18</v>
       </c>
       <c r="W79" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X79">
         <v>-0.007778</v>
@@ -24995,7 +25010,7 @@
         <v>25</v>
       </c>
       <c r="B80" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C80" s="2">
         <v>45739.36403003473</v>
@@ -25013,13 +25028,13 @@
         <v>2250</v>
       </c>
       <c r="H80" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I80" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="J80" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="K80">
         <v>111</v>
@@ -25058,7 +25073,7 @@
         <v>-17.43333333</v>
       </c>
       <c r="W80" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X80">
         <v>0.018889</v>
@@ -25090,7 +25105,7 @@
         <v>25</v>
       </c>
       <c r="B81" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C81" s="2">
         <v>45739.36411003472</v>
@@ -25108,13 +25123,13 @@
         <v>2254</v>
       </c>
       <c r="H81" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I81" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="J81" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="K81">
         <v>112</v>
@@ -25153,7 +25168,7 @@
         <v>-17.78333333</v>
       </c>
       <c r="W81" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X81">
         <v>-0.005833</v>
@@ -25185,7 +25200,7 @@
         <v>25</v>
       </c>
       <c r="B82" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C82" s="2">
         <v>45739.36441136574</v>
@@ -25203,13 +25218,13 @@
         <v>2280</v>
       </c>
       <c r="H82" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I82" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="J82" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="K82">
         <v>122</v>
@@ -25248,7 +25263,7 @@
         <v>-18.2</v>
       </c>
       <c r="W82" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X82">
         <v>-0.013889</v>
@@ -25280,7 +25295,7 @@
         <v>25</v>
       </c>
       <c r="B83" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C83" s="2">
         <v>45739.36444579861</v>
@@ -25298,13 +25313,13 @@
         <v>2284</v>
       </c>
       <c r="H83" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I83" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="J83" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="K83">
         <v>126</v>
@@ -25343,7 +25358,7 @@
         <v>-18.13333333</v>
       </c>
       <c r="W83" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X83">
         <v>0.002222</v>
@@ -25375,7 +25390,7 @@
         <v>25</v>
       </c>
       <c r="B84" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C84" s="2">
         <v>45739.36472903935</v>
@@ -25393,13 +25408,13 @@
         <v>2310</v>
       </c>
       <c r="H84" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I84" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="J84" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="K84">
         <v>120</v>
@@ -25438,7 +25453,7 @@
         <v>-17.43333333</v>
       </c>
       <c r="W84" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X84">
         <v>0.023333</v>
@@ -25470,7 +25485,7 @@
         <v>25</v>
       </c>
       <c r="B85" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C85" s="2">
         <v>45739.36510489583</v>
@@ -25488,13 +25503,13 @@
         <v>2340</v>
       </c>
       <c r="H85" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I85" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="J85" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="K85">
         <v>156</v>
@@ -25533,7 +25548,7 @@
         <v>-17.4</v>
       </c>
       <c r="W85" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X85">
         <v>0.001111</v>
@@ -25565,7 +25580,7 @@
         <v>25</v>
       </c>
       <c r="B86" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C86" s="2">
         <v>45739.36514101852</v>
@@ -25583,13 +25598,13 @@
         <v>2344</v>
       </c>
       <c r="H86" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I86" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="J86" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="K86">
         <v>157</v>
@@ -25628,7 +25643,7 @@
         <v>-17.3</v>
       </c>
       <c r="W86" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X86">
         <v>0.001667</v>
@@ -25660,7 +25675,7 @@
         <v>25</v>
       </c>
       <c r="B87" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C87" s="2">
         <v>45739.36542457176</v>
@@ -25678,13 +25693,13 @@
         <v>2370</v>
       </c>
       <c r="H87" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I87" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="J87" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="K87">
         <v>154</v>
@@ -25723,7 +25738,7 @@
         <v>-15.26666667</v>
       </c>
       <c r="W87" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X87">
         <v>0.067778</v>
@@ -25755,7 +25770,7 @@
         <v>25</v>
       </c>
       <c r="B88" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C88" s="2">
         <v>45739.36550032407</v>
@@ -25773,13 +25788,13 @@
         <v>2374</v>
       </c>
       <c r="H88" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I88" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="J88" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="K88">
         <v>156</v>
@@ -25818,7 +25833,7 @@
         <v>-14.46666667</v>
       </c>
       <c r="W88" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X88">
         <v>0.026667</v>
@@ -25850,7 +25865,7 @@
         <v>25</v>
       </c>
       <c r="B89" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C89" s="2">
         <v>45739.36580111111</v>
@@ -25868,13 +25883,13 @@
         <v>2400</v>
       </c>
       <c r="H89" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I89" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J89" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="K89">
         <v>170</v>
@@ -25913,7 +25928,7 @@
         <v>-15.3</v>
       </c>
       <c r="W89" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X89">
         <v>-0.027778</v>
@@ -25945,7 +25960,7 @@
         <v>25</v>
       </c>
       <c r="B90" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C90" s="2">
         <v>45739.36583591435</v>
@@ -25963,13 +25978,13 @@
         <v>2404</v>
       </c>
       <c r="H90" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I90" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="J90" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="K90">
         <v>169</v>
@@ -26008,7 +26023,7 @@
         <v>-16.1</v>
       </c>
       <c r="W90" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X90">
         <v>-0.026667</v>
@@ -26040,7 +26055,7 @@
         <v>25</v>
       </c>
       <c r="B91" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C91" s="2">
         <v>45739.36612013889</v>
@@ -26058,13 +26073,13 @@
         <v>2430</v>
       </c>
       <c r="H91" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I91" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="J91" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="K91">
         <v>162</v>
@@ -26103,7 +26118,7 @@
         <v>-16.63333333</v>
       </c>
       <c r="W91" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X91">
         <v>-0.017778</v>
@@ -26135,7 +26150,7 @@
         <v>25</v>
       </c>
       <c r="B92" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C92" s="2">
         <v>45739.36619440973</v>
@@ -26153,13 +26168,13 @@
         <v>2434</v>
       </c>
       <c r="H92" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I92" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="J92" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="K92">
         <v>170</v>
@@ -26198,7 +26213,7 @@
         <v>-16.86666667</v>
       </c>
       <c r="W92" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X92">
         <v>-0.007778</v>
@@ -26230,7 +26245,7 @@
         <v>25</v>
       </c>
       <c r="B93" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C93" s="2">
         <v>45739.36649628473</v>
@@ -26248,13 +26263,13 @@
         <v>2460</v>
       </c>
       <c r="H93" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I93" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="J93" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="K93">
         <v>173</v>
@@ -26293,7 +26308,7 @@
         <v>-18.4</v>
       </c>
       <c r="W93" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X93">
         <v>-0.051111</v>
@@ -26325,7 +26340,7 @@
         <v>25</v>
       </c>
       <c r="B94" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C94" s="2">
         <v>45739.36651325232</v>
@@ -26343,13 +26358,13 @@
         <v>2464</v>
       </c>
       <c r="H94" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I94" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="J94" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="K94">
         <v>172</v>
@@ -26388,7 +26403,7 @@
         <v>-18.63333333</v>
       </c>
       <c r="W94" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X94">
         <v>-0.007778</v>
@@ -26420,7 +26435,7 @@
         <v>25</v>
       </c>
       <c r="B95" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C95" s="2">
         <v>45739.36681497685</v>
@@ -26438,13 +26453,13 @@
         <v>2490</v>
       </c>
       <c r="H95" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I95" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="J95" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="K95">
         <v>197</v>
@@ -26483,7 +26498,7 @@
         <v>-19.3</v>
       </c>
       <c r="W95" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X95">
         <v>-0.022222</v>
@@ -26515,7 +26530,7 @@
         <v>25</v>
       </c>
       <c r="B96" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C96" s="2">
         <v>45739.36688947917</v>
@@ -26533,13 +26548,13 @@
         <v>2494</v>
       </c>
       <c r="H96" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I96" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="J96" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="K96">
         <v>197</v>
@@ -26578,7 +26593,7 @@
         <v>-18.93333333</v>
       </c>
       <c r="W96" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X96">
         <v>0.012222</v>
@@ -26610,7 +26625,7 @@
         <v>25</v>
       </c>
       <c r="B97" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C97" s="2">
         <v>45739.36719096065</v>
@@ -26628,13 +26643,13 @@
         <v>2520</v>
       </c>
       <c r="H97" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I97" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="J97" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="K97">
         <v>181</v>
@@ -26673,7 +26688,7 @@
         <v>-16.96666667</v>
       </c>
       <c r="W97" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X97">
         <v>0.065556</v>
@@ -26705,7 +26720,7 @@
         <v>25</v>
       </c>
       <c r="B98" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C98" s="2">
         <v>45739.3672255787</v>
@@ -26723,13 +26738,13 @@
         <v>2524</v>
       </c>
       <c r="H98" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I98" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="J98" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="K98">
         <v>179</v>
@@ -26768,7 +26783,7 @@
         <v>-17.23333333</v>
       </c>
       <c r="W98" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X98">
         <v>-0.008888999999999999</v>
@@ -26800,7 +26815,7 @@
         <v>25</v>
       </c>
       <c r="B99" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C99" s="2">
         <v>45739.36793391204</v>
@@ -26818,13 +26833,13 @@
         <v>2584</v>
       </c>
       <c r="H99" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I99" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="J99" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="K99">
         <v>164</v>
@@ -26863,7 +26878,7 @@
         <v>-4.01666667</v>
       </c>
       <c r="W99" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X99">
         <v>0.220278</v>
@@ -26895,7 +26910,7 @@
         <v>25</v>
       </c>
       <c r="B100" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C100" s="2">
         <v>45739.36820517361</v>
@@ -26913,13 +26928,13 @@
         <v>2610</v>
       </c>
       <c r="H100" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I100" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="J100" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K100">
         <v>201</v>
@@ -26958,7 +26973,7 @@
         <v>-4.07777778</v>
       </c>
       <c r="W100" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X100">
         <v>-0.000679</v>

--- a/www/flightdata/xlsx/eoss-369.xlsx
+++ b/www/flightdata/xlsx/eoss-369.xlsx
@@ -2367,7 +2367,7 @@
         <v>29112.97</v>
       </c>
       <c r="I2">
-        <v>395</v>
+        <v>258</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
